--- a/ブレース接合部/ブレース接合部の検討.xlsx
+++ b/ブレース接合部/ブレース接合部の検討.xlsx
@@ -1,31 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a44ef2ff30a9bf4/00_24webclamp/00_戸田建設九州支店某案件495/02設計資料/ブレース接合部/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TSUBOIK\Documents\git\00KeisansyoTemplate\ブレース接合部\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2434" documentId="14_{AB0E8A8A-5925-4D04-AFBE-E2AF64A40BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00801CBB-E199-4250-AFF8-20ECC7F92CCB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB88FFC-0B0C-40D6-9BBF-B9D1E7AD7526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="-120" windowWidth="27420" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="-120" windowWidth="27420" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="i" sheetId="14" r:id="rId1"/>
-    <sheet name="Nd" sheetId="13" r:id="rId2"/>
-    <sheet name="bolt_y" sheetId="1" r:id="rId3"/>
-    <sheet name="gpl_y" sheetId="2" r:id="rId4"/>
-    <sheet name="weld_y" sheetId="3" r:id="rId5"/>
-    <sheet name="beam_y" sheetId="4" r:id="rId6"/>
-    <sheet name="bolt_u" sheetId="6" r:id="rId7"/>
-    <sheet name="gpl_u" sheetId="7" r:id="rId8"/>
-    <sheet name="weld_u" sheetId="8" r:id="rId9"/>
-    <sheet name="brace_u" sheetId="9" r:id="rId10"/>
-    <sheet name="wcs_y" sheetId="10" r:id="rId11"/>
-    <sheet name="wcs_u" sheetId="11" r:id="rId12"/>
-    <sheet name="bolt_qa" sheetId="12" r:id="rId13"/>
+    <sheet name="シートの説明" sheetId="15" r:id="rId1"/>
+    <sheet name="section" sheetId="14" r:id="rId2"/>
+    <sheet name="Nd" sheetId="13" r:id="rId3"/>
+    <sheet name="bolt_y" sheetId="1" r:id="rId4"/>
+    <sheet name="gpl_y" sheetId="2" r:id="rId5"/>
+    <sheet name="weld_y" sheetId="3" r:id="rId6"/>
+    <sheet name="beam_y" sheetId="4" r:id="rId7"/>
+    <sheet name="bolt_u" sheetId="6" r:id="rId8"/>
+    <sheet name="gpl_u" sheetId="7" r:id="rId9"/>
+    <sheet name="weld_u" sheetId="8" r:id="rId10"/>
+    <sheet name="brace_u" sheetId="9" r:id="rId11"/>
+    <sheet name="bolt_qa" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -81,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="123">
   <si>
     <t>ボルト本数</t>
   </si>
@@ -209,10 +208,6 @@
 [kN]</t>
   </si>
   <si>
-    <t>ブレース材短期許容耐力
-[kN]</t>
-  </si>
-  <si>
     <t>α</t>
   </si>
   <si>
@@ -266,22 +261,6 @@
   </si>
   <si>
     <t>V4</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>金物/SPL引張耐力
-[kN]</t>
-    <rPh sb="0" eb="2">
-      <t>カナモノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>金物/SPL終局耐力
-[kN]</t>
-    <rPh sb="0" eb="2">
-      <t>カナモノ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -664,6 +643,279 @@
     <t>G88MB</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>断面2次モーメント[cm4]</t>
+    <rPh sb="0" eb="2">
+      <t>ダンメン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>section</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Nd</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bolt_y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gpl_y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>weld_y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>beam_y</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bolt_u</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>gpl_u</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>weld_u</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>brace_u</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bolt_qa</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各シートの説明</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設計軸力の計算</t>
+    <rPh sb="0" eb="2">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>リョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>母材の断面積や断面2次半径の計算</t>
+    <rPh sb="0" eb="2">
+      <t>ボザイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダンメン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>セキ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ダンメン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンケイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボルトの許容応力度計算</t>
+    <rPh sb="4" eb="6">
+      <t>キョヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウリョク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GPLの許容応力度計算</t>
+    <rPh sb="4" eb="6">
+      <t>キョヨウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オウリョク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GPL溶接部の許容応力度計算</t>
+    <rPh sb="3" eb="5">
+      <t>ヨウセツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>キョヨウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オウリョク</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>受梁端部接合部の許容応力度計算</t>
+    <rPh sb="0" eb="1">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ハリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タンブ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セツゴウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キョヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>オウリョク</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ド</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボルトの保有耐力接合の検討</t>
+    <rPh sb="4" eb="6">
+      <t>ホユウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セツゴウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GPLの保有耐力接合の検討</t>
+    <rPh sb="4" eb="6">
+      <t>ホユウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>セツゴウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GPL溶接部の保有耐力接合の検討</t>
+    <rPh sb="3" eb="5">
+      <t>ヨウセツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ホユウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セツゴウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>母材の保有耐力接合の検討</t>
+    <rPh sb="0" eb="2">
+      <t>ボザイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホユウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>セツゴウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各ボルトの耐力</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>タイリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -673,7 +925,7 @@
     <numFmt numFmtId="176" formatCode="0.0"/>
     <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -728,8 +980,23 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans CJK JP"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans CJK JP"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -763,6 +1030,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -950,7 +1241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -965,9 +1256,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1127,54 +1415,25 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1567,475 +1826,106 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B7E9DBE-FFD1-4100-A239-982A73A53C23}">
-  <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{381CD668-A464-4109-9C7B-5A66168949A8}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="6" width="12.7109375" style="53"/>
-    <col min="7" max="7" width="15.42578125" style="53" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="12.7109375" style="53"/>
+    <col min="1" max="1" width="15.28515625" style="59" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55" t="s">
-        <v>75</v>
-      </c>
-      <c r="L1" s="21" t="str">
-        <f>A1</f>
-        <v>符号</v>
-      </c>
-      <c r="M1" s="21" t="str">
-        <f>E1</f>
-        <v>断面</v>
-      </c>
-      <c r="N1" s="21" t="str">
-        <f>F1</f>
-        <v>断面積
-[cm2]</v>
-      </c>
-      <c r="O1" s="21" t="str">
-        <f>G1</f>
-        <v>使用ボルト</v>
-      </c>
-      <c r="P1" s="21" t="str">
-        <f>H1</f>
-        <v>引張側有効断面積
-[cm2]</v>
-      </c>
-      <c r="Q1" s="21" t="str">
-        <f t="shared" ref="Q1:Q7" si="0">J1</f>
-        <v>断面2次半径
-[cm]</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="35">
-        <v>133.5</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" s="35">
-        <f t="shared" ref="H2:H7" si="1">F2</f>
-        <v>133.5</v>
-      </c>
-      <c r="I2" s="57">
-        <f>2/3*(15*150^3+(305-15)*15^3)/10000</f>
-        <v>3440.25</v>
-      </c>
-      <c r="J2" s="31">
-        <f>SQRT(I2/F2)</f>
-        <v>5.0763828580346768</v>
-      </c>
-      <c r="L2" s="17" t="str">
-        <f t="shared" ref="L2:L7" si="2">A2</f>
-        <v>V0</v>
-      </c>
-      <c r="M2" s="17" t="str">
-        <f t="shared" ref="M2:O7" si="3">E2</f>
-        <v>2CT-150x305x15x15</v>
-      </c>
-      <c r="N2" s="17">
-        <f t="shared" si="3"/>
-        <v>133.5</v>
-      </c>
-      <c r="O2" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>2x13-M22(S10T)</v>
-      </c>
-      <c r="P2" s="17" t="str">
-        <f>H2&amp;" ("&amp;ROUND(H2/F2*100, 1)&amp;"%)"</f>
-        <v>133.5 (100%)</v>
-      </c>
-      <c r="Q2" s="56">
-        <f t="shared" si="0"/>
-        <v>5.0763828580346768</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="35">
-        <v>91.43</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="H3" s="35">
-        <f t="shared" si="1"/>
-        <v>91.43</v>
-      </c>
-      <c r="I3" s="57">
-        <f>2/3*(9*150^3+(305-9)*14^3)/10000</f>
-        <v>2079.1482666666666</v>
-      </c>
-      <c r="J3" s="31">
-        <f>SQRT(I3/F3)</f>
-        <v>4.7686820872258195</v>
-      </c>
-      <c r="L3" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>V1</v>
-      </c>
-      <c r="M3" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>2CT-125x250x9x14</v>
-      </c>
-      <c r="N3" s="17">
-        <f t="shared" si="3"/>
-        <v>91.43</v>
-      </c>
-      <c r="O3" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>2x12-M20(S10T)</v>
-      </c>
-      <c r="P3" s="17" t="str">
-        <f t="shared" ref="P3:P8" si="4">H3&amp;" ("&amp;ROUND(H3/F3*100, 1)&amp;"%)"</f>
-        <v>91.43 (100%)</v>
-      </c>
-      <c r="Q3" s="56">
-        <f t="shared" si="0"/>
-        <v>4.7686820872258195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B4" s="8">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8">
-        <v>22</v>
-      </c>
-      <c r="D4" s="8">
-        <v>300</v>
-      </c>
-      <c r="E4" s="35" t="str">
-        <f t="shared" ref="E4:E5" si="5">"PL-"&amp;C4&amp;"x"&amp;D4</f>
-        <v>PL-22x300</v>
-      </c>
-      <c r="F4" s="35">
-        <f t="shared" ref="F4:F6" si="6">B4*C4*D4/100</f>
-        <v>66</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="H4" s="35">
-        <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-      <c r="I4" s="34">
-        <f t="shared" ref="I4:I7" si="7">D4*(B4*C4)^3/12/10000</f>
-        <v>26.62</v>
-      </c>
-      <c r="J4" s="31">
-        <f t="shared" ref="J4:J7" si="8">SQRT(I4/F4)</f>
-        <v>0.63508529610858833</v>
-      </c>
-      <c r="L4" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>V2</v>
-      </c>
-      <c r="M4" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>PL-22x300</v>
-      </c>
-      <c r="N4" s="17">
-        <f t="shared" si="3"/>
-        <v>66</v>
-      </c>
-      <c r="O4" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>2x11-M20(S10T)</v>
-      </c>
-      <c r="P4" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>66 (100%)</v>
-      </c>
-      <c r="Q4" s="56">
-        <f t="shared" si="0"/>
-        <v>0.63508529610858833</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="8">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8">
-        <v>25</v>
-      </c>
-      <c r="D5" s="8">
-        <v>200</v>
-      </c>
-      <c r="E5" s="35" t="str">
-        <f t="shared" si="5"/>
-        <v>PL-25x200</v>
-      </c>
-      <c r="F5" s="35">
-        <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="H5" s="35">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="I5" s="34">
-        <f t="shared" si="7"/>
-        <v>26.041666666666664</v>
-      </c>
-      <c r="J5" s="31">
-        <f t="shared" si="8"/>
-        <v>0.72168783648703216</v>
-      </c>
-      <c r="L5" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>V3</v>
-      </c>
-      <c r="M5" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>PL-25x200</v>
-      </c>
-      <c r="N5" s="17">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="O5" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>2x10-M20(S10T)</v>
-      </c>
-      <c r="P5" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>50 (100%)</v>
-      </c>
-      <c r="Q5" s="56">
-        <f t="shared" si="0"/>
-        <v>0.72168783648703216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8">
-        <v>25</v>
-      </c>
-      <c r="D6" s="8">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="60" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="63" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="61" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="B10" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="35" t="str">
-        <f>"PL-"&amp;C6&amp;"x"&amp;D6</f>
-        <v>PL-25x120</v>
-      </c>
-      <c r="F6" s="35">
-        <f t="shared" si="6"/>
-        <v>30</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H6" s="35">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="I6" s="34">
-        <f t="shared" si="7"/>
-        <v>15.625</v>
-      </c>
-      <c r="J6" s="31">
-        <f t="shared" si="8"/>
-        <v>0.72168783648703227</v>
-      </c>
-      <c r="L6" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>V4</v>
-      </c>
-      <c r="M6" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>PL-25x120</v>
-      </c>
-      <c r="N6" s="17">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="O6" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>2x6-M22(S10T)</v>
-      </c>
-      <c r="P6" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>30 (100%)</v>
-      </c>
-      <c r="Q6" s="56">
-        <f t="shared" si="0"/>
-        <v>0.72168783648703227</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="8">
-        <v>1</v>
-      </c>
-      <c r="C7" s="8">
-        <v>25</v>
-      </c>
-      <c r="D7" s="8">
-        <v>100</v>
-      </c>
-      <c r="E7" s="35" t="str">
-        <f>"PL-"&amp;C7&amp;"x"&amp;D7</f>
-        <v>PL-25x100</v>
-      </c>
-      <c r="F7" s="35">
-        <f>B7*C7*D7/100</f>
-        <v>25</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="35">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="I7" s="34">
-        <f t="shared" si="7"/>
-        <v>13.020833333333332</v>
-      </c>
-      <c r="J7" s="31">
-        <f t="shared" si="8"/>
-        <v>0.72168783648703216</v>
-      </c>
-      <c r="L7" s="17" t="str">
-        <f t="shared" si="2"/>
-        <v>V5</v>
-      </c>
-      <c r="M7" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>PL-25x100</v>
-      </c>
-      <c r="N7" s="17">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="O7" s="17" t="str">
-        <f t="shared" si="3"/>
-        <v>2x5-M22(S10T)</v>
-      </c>
-      <c r="P7" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>25 (100%)</v>
-      </c>
-      <c r="Q7" s="56">
-        <f t="shared" si="0"/>
-        <v>0.72168783648703216</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="8">
-        <v>2</v>
-      </c>
-      <c r="C8" s="8">
-        <v>22</v>
-      </c>
-      <c r="D8" s="8">
-        <v>230</v>
-      </c>
-      <c r="E8" s="35" t="str">
-        <f>B8&amp;"PL-"&amp;C8&amp;"x"&amp;D8</f>
-        <v>2PL-22x230</v>
-      </c>
-      <c r="F8" s="35">
-        <f>B8*C8*D8/100</f>
-        <v>101.2</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H8" s="35">
-        <f>F8-2*C8*24/100</f>
-        <v>90.64</v>
-      </c>
-      <c r="I8" s="34">
-        <f t="shared" ref="I8" si="9">D8*(B8*C8)^3/12/10000</f>
-        <v>163.26933333333332</v>
-      </c>
-      <c r="J8" s="31">
-        <f t="shared" ref="J8" si="10">SQRT(I8/F8)</f>
-        <v>1.2701705922171767</v>
-      </c>
-      <c r="L8" s="17" t="str">
-        <f t="shared" ref="L8" si="11">A8</f>
-        <v>V11</v>
-      </c>
-      <c r="M8" s="17" t="str">
-        <f t="shared" ref="M8" si="12">E8</f>
-        <v>2PL-22x230</v>
-      </c>
-      <c r="N8" s="17">
-        <f t="shared" ref="N8" si="13">F8</f>
-        <v>101.2</v>
-      </c>
-      <c r="O8" s="17" t="str">
-        <f t="shared" ref="O8" si="14">G8</f>
-        <v>2x13-M22(S10T)</v>
-      </c>
-      <c r="P8" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>90.64 (89.6%)</v>
-      </c>
-      <c r="Q8" s="56">
-        <f t="shared" ref="Q8" si="15">J8</f>
-        <v>1.2701705922171767</v>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="62" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="62" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="64" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="64" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2045,7 +1935,10 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324BAFE0-36E2-4B55-AFE7-9FD7B71A8516}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4716E361-ED6F-4B3B-89DF-4B973A4AF614}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -2053,17 +1946,17 @@
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>71</v>
+      <c r="B1" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>5</v>
@@ -2073,209 +1966,222 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="str">
+      <c r="A2" s="28" t="str">
         <f>Nd!A2</f>
         <v>V0</v>
       </c>
-      <c r="B2" s="34">
+      <c r="B2" s="33">
         <f>Nd!H2</f>
         <v>5206.5</v>
       </c>
-      <c r="C2" s="37">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4">
-        <v>490</v>
-      </c>
-      <c r="E2" s="27">
-        <f t="shared" ref="E2:E7" si="0">D2*C2*100/1000</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="30" t="e">
+      <c r="C2" s="32">
+        <f>weld_y!E2*weld_y!G2/100</f>
+        <v>250</v>
+      </c>
+      <c r="D2" s="5">
+        <f t="shared" ref="D2:D7" si="0">490/SQRT(3)</f>
+        <v>282.90163190291662</v>
+      </c>
+      <c r="E2" s="26">
+        <f t="shared" ref="E2:E7" si="1">D2*C2*100/1000</f>
+        <v>7072.5407975729167</v>
+      </c>
+      <c r="F2" s="29">
         <f>B2/E2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G2" s="4" t="e">
-        <f t="shared" ref="G2:G8" si="1">IF(F2&lt;1, "OK", "NG")</f>
-        <v>#DIV/0!</v>
+        <v>0.73615694119243735</v>
+      </c>
+      <c r="G2" s="4" t="str">
+        <f t="shared" ref="G2:G8" si="2">IF(F2&lt;1, "OK", "NG")</f>
+        <v>OK</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="str">
+      <c r="A3" s="28" t="str">
         <f>Nd!A3</f>
         <v>V1</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="33">
         <f>Nd!H3</f>
         <v>3565.77</v>
       </c>
-      <c r="C3" s="37">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>490</v>
-      </c>
-      <c r="E3" s="27">
+      <c r="C3" s="32">
+        <f>weld_y!E3*weld_y!G3/100</f>
+        <v>171</v>
+      </c>
+      <c r="D3" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F3" s="30" t="e">
-        <f t="shared" ref="F3:F7" si="2">B3/E3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G3" s="4" t="e">
+        <v>282.90163190291662</v>
+      </c>
+      <c r="E3" s="26">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>4837.6179055398752</v>
+      </c>
+      <c r="F3" s="29">
+        <f t="shared" ref="F3:F7" si="3">B3/E3</f>
+        <v>0.73709211219774129</v>
+      </c>
+      <c r="G3" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v>OK</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="str">
+      <c r="A4" s="28" t="str">
         <f>Nd!A4</f>
         <v>V2</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="33">
         <f>Nd!H4</f>
         <v>2574</v>
       </c>
-      <c r="C4" s="37">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>490</v>
-      </c>
-      <c r="E4" s="27">
+      <c r="C4" s="32">
+        <f>weld_y!E4*weld_y!G4/100</f>
+        <v>121.96799999999998</v>
+      </c>
+      <c r="D4" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F4" s="30" t="e">
+        <v>282.90163190291662</v>
+      </c>
+      <c r="E4" s="26">
+        <f t="shared" si="1"/>
+        <v>3450.4946239934925</v>
+      </c>
+      <c r="F4" s="29">
+        <f t="shared" si="3"/>
+        <v>0.74598000591026414</v>
+      </c>
+      <c r="G4" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G4" s="4" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="str">
+      <c r="A5" s="28" t="str">
         <f>Nd!A5</f>
         <v>V3</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="33">
         <f>Nd!H5</f>
         <v>1950</v>
       </c>
-      <c r="C5" s="37">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>490</v>
-      </c>
-      <c r="E5" s="27">
+      <c r="C5" s="32">
+        <f>weld_y!E5*weld_y!G5/100</f>
+        <v>88.367999999999995</v>
+      </c>
+      <c r="D5" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F5" s="30" t="e">
+        <v>282.90163190291662</v>
+      </c>
+      <c r="E5" s="26">
+        <f t="shared" si="1"/>
+        <v>2499.9451407996935</v>
+      </c>
+      <c r="F5" s="29">
+        <f t="shared" si="3"/>
+        <v>0.78001711644609339</v>
+      </c>
+      <c r="G5" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="4" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="str">
+      <c r="A6" s="28" t="str">
         <f>Nd!A6</f>
         <v>V4</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="33">
         <f>Nd!H6</f>
         <v>1170</v>
       </c>
-      <c r="C6" s="37">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>490</v>
-      </c>
-      <c r="E6" s="27">
+      <c r="C6" s="32">
+        <f>weld_y!E6*weld_y!G6/100</f>
+        <v>54.767999999999994</v>
+      </c>
+      <c r="D6" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="30" t="e">
+        <v>282.90163190291662</v>
+      </c>
+      <c r="E6" s="26">
+        <f t="shared" si="1"/>
+        <v>1549.3956576058936</v>
+      </c>
+      <c r="F6" s="29">
+        <f t="shared" si="3"/>
+        <v>0.7551331348171384</v>
+      </c>
+      <c r="G6" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G6" s="4" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="str">
+      <c r="A7" s="28" t="str">
         <f>Nd!A7</f>
         <v>V5</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="33">
         <f>Nd!H7</f>
         <v>975</v>
       </c>
-      <c r="C7" s="37">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>490</v>
-      </c>
-      <c r="E7" s="27">
+      <c r="C7" s="32">
+        <f>weld_y!E7*weld_y!G7/100</f>
+        <v>46.367999999999995</v>
+      </c>
+      <c r="D7" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="30" t="e">
+        <v>282.90163190291662</v>
+      </c>
+      <c r="E7" s="26">
+        <f t="shared" si="1"/>
+        <v>1311.7582868074437</v>
+      </c>
+      <c r="F7" s="29">
+        <f t="shared" si="3"/>
+        <v>0.74327717980189345</v>
+      </c>
+      <c r="G7" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G7" s="4" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="str">
+      <c r="A8" s="28" t="str">
         <f>Nd!A8</f>
         <v>V11</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="33">
         <f>Nd!H8</f>
         <v>5343.36</v>
       </c>
-      <c r="C8" s="37">
-        <f>i!H8</f>
-        <v>90.64</v>
-      </c>
-      <c r="D8" s="4">
-        <v>590</v>
-      </c>
-      <c r="E8" s="27">
-        <f t="shared" ref="E8" si="3">D8*C8*100/1000</f>
-        <v>5347.76</v>
-      </c>
-      <c r="F8" s="30">
-        <f t="shared" ref="F8" si="4">B8/E8</f>
-        <v>0.99917722560473909</v>
+      <c r="C8" s="32">
+        <f>weld_y!E8*weld_y!G8/100</f>
+        <v>237.5</v>
+      </c>
+      <c r="D8" s="5">
+        <f>490/SQRT(3)</f>
+        <v>282.90163190291662</v>
+      </c>
+      <c r="E8" s="26">
+        <f t="shared" ref="E8" si="4">D8*C8*100/1000</f>
+        <v>6718.9137576942694</v>
+      </c>
+      <c r="F8" s="29">
+        <f t="shared" ref="F8" si="5">B8/E8</f>
+        <v>0.79527140735821578</v>
       </c>
       <c r="G8" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="G2:G8">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="NG">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="NG">
       <formula>NOT(ISERROR(SEARCH("NG",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2284,47 +2190,241 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBAB8398-6CF2-4EBF-96C2-DCF768B2B1B6}">
-  <dimension ref="A1:D2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324BAFE0-36E2-4B55-AFE7-9FD7B71A8516}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8"/>
-      <c r="B2" s="5">
-        <f>bolt_y!B6</f>
+    <row r="2" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="str">
+        <f>Nd!A2</f>
+        <v>V0</v>
+      </c>
+      <c r="B2" s="33">
+        <f>Nd!H2</f>
+        <v>5206.5</v>
+      </c>
+      <c r="C2" s="36">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>490</v>
+      </c>
+      <c r="E2" s="26">
+        <f t="shared" ref="E2:E7" si="0">D2*C2*100/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="29" t="e">
+        <f>B2/E2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G2" s="4" t="e">
+        <f t="shared" ref="G2:G8" si="1">IF(F2&lt;1, "OK", "NG")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="28" t="str">
+        <f>Nd!A3</f>
+        <v>V1</v>
+      </c>
+      <c r="B3" s="33">
+        <f>Nd!H3</f>
+        <v>3565.77</v>
+      </c>
+      <c r="C3" s="36">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>490</v>
+      </c>
+      <c r="E3" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F3" s="29" t="e">
+        <f t="shared" ref="F3:F7" si="2">B3/E3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G3" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="28" t="str">
+        <f>Nd!A4</f>
+        <v>V2</v>
+      </c>
+      <c r="B4" s="33">
+        <f>Nd!H4</f>
+        <v>2574</v>
+      </c>
+      <c r="C4" s="36">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>490</v>
+      </c>
+      <c r="E4" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="29" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G4" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="28" t="str">
+        <f>Nd!A5</f>
+        <v>V3</v>
+      </c>
+      <c r="B5" s="33">
+        <f>Nd!H5</f>
+        <v>1950</v>
+      </c>
+      <c r="C5" s="36">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <v>490</v>
+      </c>
+      <c r="E5" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="29" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G5" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="28" t="str">
+        <f>Nd!A6</f>
+        <v>V4</v>
+      </c>
+      <c r="B6" s="33">
+        <f>Nd!H6</f>
+        <v>1170</v>
+      </c>
+      <c r="C6" s="36">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>490</v>
+      </c>
+      <c r="E6" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="29" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G6" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="28" t="str">
+        <f>Nd!A7</f>
+        <v>V5</v>
+      </c>
+      <c r="B7" s="33">
+        <f>Nd!H7</f>
         <v>975</v>
       </c>
-      <c r="C2" s="9">
-        <f>2*832</f>
-        <v>1664</v>
-      </c>
-      <c r="D2" s="8" t="str">
-        <f>IF(C2&gt;B2, "OK", "NG")</f>
+      <c r="C7" s="36">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>490</v>
+      </c>
+      <c r="E7" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="29" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G7" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="28" t="str">
+        <f>Nd!A8</f>
+        <v>V11</v>
+      </c>
+      <c r="B8" s="33">
+        <f>Nd!H8</f>
+        <v>5343.36</v>
+      </c>
+      <c r="C8" s="36">
+        <f>section!H8</f>
+        <v>90.64</v>
+      </c>
+      <c r="D8" s="4">
+        <v>590</v>
+      </c>
+      <c r="E8" s="26">
+        <f t="shared" ref="E8" si="3">D8*C8*100/1000</f>
+        <v>5347.76</v>
+      </c>
+      <c r="F8" s="29">
+        <f t="shared" ref="F8" si="4">B8/E8</f>
+        <v>0.99917722560473909</v>
+      </c>
+      <c r="G8" s="4" t="str">
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="D2">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",D2)))</formula>
+  <conditionalFormatting sqref="G2:G8">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",D2)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2332,68 +2432,10 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AF53CC-09AC-45BB-8500-1B2245768137}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8"/>
-      <c r="B2" s="5">
-        <f>Nd!F$6</f>
-        <v>975</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="D2" s="5">
-        <f>2*1254</f>
-        <v>2508</v>
-      </c>
-      <c r="E2" s="6">
-        <f>Nd!H6/D2</f>
-        <v>0.46650717703349281</v>
-      </c>
-      <c r="F2" s="4" t="str">
-        <f>IF(E2&lt;1, "OK", "NG")</f>
-        <v>OK</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",F2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",F2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13509B56-E6A2-4339-8D9B-E2F8C2594B5B}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2403,269 +2445,269 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>70</v>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="42" t="str">
+      <c r="A2" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="41" t="str">
         <f>A2&amp;B2</f>
         <v>F8TM12</v>
       </c>
-      <c r="D2" s="43">
+      <c r="D2" s="42">
         <v>12.1</v>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="43">
         <v>54.2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="46" t="str">
+      <c r="C3" s="45" t="str">
         <f t="shared" ref="C3:C15" si="0">A3&amp;B3</f>
         <v>F8TM16</v>
       </c>
-      <c r="D3" s="47">
+      <c r="D3" s="46">
         <v>21.4</v>
       </c>
-      <c r="E3" s="48">
+      <c r="E3" s="47">
         <v>96.5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="46" t="str">
+      <c r="A4" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="45" t="str">
         <f t="shared" si="0"/>
         <v>F8TM20</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="46">
         <v>33.5</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="47">
         <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="46" t="str">
+      <c r="A5" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="45" t="str">
         <f t="shared" si="0"/>
         <v>F8TM22</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="46">
         <v>40.5</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="47">
         <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="46" t="str">
+      <c r="A6" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="45" t="str">
         <f t="shared" si="0"/>
         <v>F8TM24</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="46">
         <v>48.2</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="47">
         <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="46" t="str">
+      <c r="A7" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="45" t="str">
         <f t="shared" si="0"/>
         <v>F8TM27</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="46">
         <v>61</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="47">
         <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="50" t="str">
+      <c r="A8" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="49" t="str">
         <f t="shared" si="0"/>
         <v>F8TM30</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="50">
         <v>75.400000000000006</v>
       </c>
-      <c r="E8" s="52">
+      <c r="E8" s="51">
         <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="42" t="str">
+      <c r="A9" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="41" t="str">
         <f t="shared" si="0"/>
         <v>S10TM12</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="42">
         <v>17</v>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="43">
         <v>67.900000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="46" t="str">
+      <c r="A10" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="45" t="str">
         <f t="shared" si="0"/>
         <v>S10TM16</v>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="46">
         <v>30.2</v>
       </c>
-      <c r="E10" s="48">
+      <c r="E10" s="47">
         <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="46" t="str">
+      <c r="A11" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="45" t="str">
         <f t="shared" si="0"/>
         <v>S10TM20</v>
       </c>
-      <c r="D11" s="47">
+      <c r="D11" s="46">
         <v>47.1</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="47">
         <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="46" t="str">
+      <c r="A12" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="45" t="str">
         <f t="shared" si="0"/>
         <v>S10TM22</v>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="46">
         <v>57</v>
       </c>
-      <c r="E12" s="48">
+      <c r="E12" s="47">
         <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="46" t="s">
+      <c r="A13" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="46" t="str">
+      <c r="B13" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="45" t="str">
         <f t="shared" si="0"/>
         <v>S10TM24</v>
       </c>
-      <c r="D13" s="47">
+      <c r="D13" s="46">
         <v>67.900000000000006</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="47">
         <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="46" t="str">
+      <c r="A14" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="45" t="str">
         <f t="shared" si="0"/>
         <v>S10TM27</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="46">
         <v>85.9</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="47">
         <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="50" t="str">
+      <c r="A15" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="49" t="str">
         <f t="shared" si="0"/>
         <v>S10TM30</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="50">
         <v>106</v>
       </c>
-      <c r="E15" s="52">
+      <c r="E15" s="51">
         <v>424</v>
       </c>
     </row>
@@ -2676,258 +2718,480 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B37F469-DE1B-4FCA-B9FC-D097C1860EA9}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B7E9DBE-FFD1-4100-A239-982A73A53C23}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="6" width="12.7109375" style="52"/>
+    <col min="7" max="7" width="15.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="12.7109375" style="52"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="66" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" ht="49.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="20" t="str">
+        <f>A1</f>
+        <v>符号</v>
+      </c>
+      <c r="M1" s="20" t="str">
+        <f>E1</f>
+        <v>断面</v>
+      </c>
+      <c r="N1" s="20" t="str">
+        <f>F1</f>
+        <v>断面積
+[cm2]</v>
+      </c>
+      <c r="O1" s="20" t="str">
+        <f>G1</f>
+        <v>使用ボルト</v>
+      </c>
+      <c r="P1" s="20" t="str">
+        <f>H1</f>
+        <v>引張側有効断面積
+[cm2]</v>
+      </c>
+      <c r="Q1" s="20" t="str">
+        <f t="shared" ref="Q1:Q7" si="0">J1</f>
+        <v>断面2次半径
+[cm]</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="34">
+        <v>133.5</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="34">
+        <f t="shared" ref="H2:H7" si="1">F2</f>
+        <v>133.5</v>
+      </c>
+      <c r="I2" s="56">
+        <f>2/3*(15*150^3+(305-15)*15^3)/10000</f>
+        <v>3440.25</v>
+      </c>
+      <c r="J2" s="30">
+        <f>SQRT(I2/F2)</f>
+        <v>5.0763828580346768</v>
+      </c>
+      <c r="L2" s="16" t="str">
+        <f t="shared" ref="L2:L7" si="2">A2</f>
+        <v>V0</v>
+      </c>
+      <c r="M2" s="16" t="str">
+        <f t="shared" ref="M2:O7" si="3">E2</f>
+        <v>2CT-150x305x15x15</v>
+      </c>
+      <c r="N2" s="16">
+        <f t="shared" si="3"/>
+        <v>133.5</v>
+      </c>
+      <c r="O2" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>2x13-M22(S10T)</v>
+      </c>
+      <c r="P2" s="16" t="str">
+        <f>H2&amp;" ("&amp;ROUND(H2/F2*100, 1)&amp;"%)"</f>
+        <v>133.5 (100%)</v>
+      </c>
+      <c r="Q2" s="55">
+        <f t="shared" si="0"/>
+        <v>5.0763828580346768</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="34">
+        <v>91.43</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="34">
+        <f t="shared" si="1"/>
+        <v>91.43</v>
+      </c>
+      <c r="I3" s="56">
+        <f>2/3*(9*150^3+(305-9)*14^3)/10000</f>
+        <v>2079.1482666666666</v>
+      </c>
+      <c r="J3" s="30">
+        <f>SQRT(I3/F3)</f>
+        <v>4.7686820872258195</v>
+      </c>
+      <c r="L3" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>V1</v>
+      </c>
+      <c r="M3" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>2CT-125x250x9x14</v>
+      </c>
+      <c r="N3" s="16">
+        <f t="shared" si="3"/>
+        <v>91.43</v>
+      </c>
+      <c r="O3" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>2x12-M20(S10T)</v>
+      </c>
+      <c r="P3" s="16" t="str">
+        <f t="shared" ref="P3:P8" si="4">H3&amp;" ("&amp;ROUND(H3/F3*100, 1)&amp;"%)"</f>
+        <v>91.43 (100%)</v>
+      </c>
+      <c r="Q3" s="55">
+        <f t="shared" si="0"/>
+        <v>4.7686820872258195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7">
+        <v>22</v>
+      </c>
+      <c r="D4" s="7">
+        <v>300</v>
+      </c>
+      <c r="E4" s="34" t="str">
+        <f t="shared" ref="E4:E5" si="5">"PL-"&amp;C4&amp;"x"&amp;D4</f>
+        <v>PL-22x300</v>
+      </c>
+      <c r="F4" s="34">
+        <f t="shared" ref="F4:F6" si="6">B4*C4*D4/100</f>
         <v>66</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="25" t="s">
+      <c r="G4" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" s="34">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+      <c r="I4" s="33">
+        <f t="shared" ref="I4:I7" si="7">D4*(B4*C4)^3/12/10000</f>
+        <v>26.62</v>
+      </c>
+      <c r="J4" s="30">
+        <f t="shared" ref="J4:J7" si="8">SQRT(I4/F4)</f>
+        <v>0.63508529610858833</v>
+      </c>
+      <c r="L4" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>V2</v>
+      </c>
+      <c r="M4" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>PL-22x300</v>
+      </c>
+      <c r="N4" s="16">
+        <f t="shared" si="3"/>
+        <v>66</v>
+      </c>
+      <c r="O4" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>2x11-M20(S10T)</v>
+      </c>
+      <c r="P4" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>66 (100%)</v>
+      </c>
+      <c r="Q4" s="55">
+        <f t="shared" si="0"/>
+        <v>0.63508529610858833</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="7">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7">
+        <v>25</v>
+      </c>
+      <c r="D5" s="7">
+        <v>200</v>
+      </c>
+      <c r="E5" s="34" t="str">
+        <f t="shared" si="5"/>
+        <v>PL-25x200</v>
+      </c>
+      <c r="F5" s="34">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="34">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="I5" s="33">
+        <f t="shared" si="7"/>
+        <v>26.041666666666664</v>
+      </c>
+      <c r="J5" s="30">
+        <f t="shared" si="8"/>
+        <v>0.72168783648703216</v>
+      </c>
+      <c r="L5" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>V3</v>
+      </c>
+      <c r="M5" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>PL-25x200</v>
+      </c>
+      <c r="N5" s="16">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="O5" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>2x10-M20(S10T)</v>
+      </c>
+      <c r="P5" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>50 (100%)</v>
+      </c>
+      <c r="Q5" s="55">
+        <f t="shared" si="0"/>
+        <v>0.72168783648703216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>25</v>
+      </c>
+      <c r="D6" s="7">
+        <v>120</v>
+      </c>
+      <c r="E6" s="34" t="str">
+        <f>"PL-"&amp;C6&amp;"x"&amp;D6</f>
+        <v>PL-25x120</v>
+      </c>
+      <c r="F6" s="34">
+        <f t="shared" si="6"/>
+        <v>30</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="34">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="I6" s="33">
+        <f t="shared" si="7"/>
+        <v>15.625</v>
+      </c>
+      <c r="J6" s="30">
+        <f t="shared" si="8"/>
+        <v>0.72168783648703227</v>
+      </c>
+      <c r="L6" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>V4</v>
+      </c>
+      <c r="M6" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>PL-25x120</v>
+      </c>
+      <c r="N6" s="16">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="O6" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>2x6-M22(S10T)</v>
+      </c>
+      <c r="P6" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>30 (100%)</v>
+      </c>
+      <c r="Q6" s="55">
+        <f t="shared" si="0"/>
+        <v>0.72168783648703227</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="str">
-        <f>i!A2</f>
-        <v>V0</v>
-      </c>
-      <c r="B2" s="4">
-        <f>i!F2</f>
-        <v>133.5</v>
-      </c>
-      <c r="C2" s="58">
-        <f>i!H2/i!F2</f>
+      <c r="B7" s="7">
         <v>1</v>
       </c>
-      <c r="D2" s="4">
-        <v>325</v>
-      </c>
-      <c r="E2" s="27">
-        <f>B2*100*C2*D2/1000</f>
-        <v>4338.75</v>
-      </c>
-      <c r="F2" s="27">
-        <f t="shared" ref="F2:F8" si="0">B2*100*D2/1000</f>
-        <v>4338.75</v>
-      </c>
-      <c r="G2" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="H2" s="27">
-        <f t="shared" ref="H2:H8" si="1">G2*F2</f>
-        <v>5206.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="str">
-        <f>i!A3</f>
-        <v>V1</v>
-      </c>
-      <c r="B3" s="4">
-        <f>i!F3</f>
-        <v>91.43</v>
-      </c>
-      <c r="C3" s="58">
-        <f>i!H3/i!F3</f>
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
-        <v>325</v>
-      </c>
-      <c r="E3" s="27">
-        <f t="shared" ref="E3:E8" si="2">B3*100*C3*D3/1000</f>
-        <v>2971.4749999999999</v>
-      </c>
-      <c r="F3" s="27">
+      <c r="C7" s="7">
+        <v>25</v>
+      </c>
+      <c r="D7" s="7">
+        <v>100</v>
+      </c>
+      <c r="E7" s="34" t="str">
+        <f>"PL-"&amp;C7&amp;"x"&amp;D7</f>
+        <v>PL-25x100</v>
+      </c>
+      <c r="F7" s="34">
+        <f>B7*C7*D7/100</f>
+        <v>25</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="34">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="I7" s="33">
+        <f t="shared" si="7"/>
+        <v>13.020833333333332</v>
+      </c>
+      <c r="J7" s="30">
+        <f t="shared" si="8"/>
+        <v>0.72168783648703216</v>
+      </c>
+      <c r="L7" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>V5</v>
+      </c>
+      <c r="M7" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>PL-25x100</v>
+      </c>
+      <c r="N7" s="16">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="O7" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>2x5-M22(S10T)</v>
+      </c>
+      <c r="P7" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>25 (100%)</v>
+      </c>
+      <c r="Q7" s="55">
         <f t="shared" si="0"/>
-        <v>2971.4749999999999</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="H3" s="27">
-        <f t="shared" si="1"/>
-        <v>3565.77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="str">
-        <f>i!A4</f>
-        <v>V2</v>
-      </c>
-      <c r="B4" s="4">
-        <f>i!F4</f>
-        <v>66</v>
-      </c>
-      <c r="C4" s="58">
-        <f>i!H4/i!F4</f>
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
-        <v>325</v>
-      </c>
-      <c r="E4" s="27">
-        <f t="shared" si="2"/>
-        <v>2145</v>
-      </c>
-      <c r="F4" s="27">
-        <f t="shared" si="0"/>
-        <v>2145</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="H4" s="27">
-        <f t="shared" si="1"/>
-        <v>2574</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="str">
-        <f>i!A5</f>
-        <v>V3</v>
-      </c>
-      <c r="B5" s="4">
-        <f>i!F5</f>
-        <v>50</v>
-      </c>
-      <c r="C5" s="58">
-        <f>i!H5/i!F5</f>
-        <v>1</v>
-      </c>
-      <c r="D5" s="4">
-        <v>325</v>
-      </c>
-      <c r="E5" s="27">
-        <f t="shared" si="2"/>
-        <v>1625</v>
-      </c>
-      <c r="F5" s="27">
-        <f t="shared" si="0"/>
-        <v>1625</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="H5" s="27">
-        <f t="shared" si="1"/>
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="str">
-        <f>i!A6</f>
-        <v>V4</v>
-      </c>
-      <c r="B6" s="4">
-        <f>i!F6</f>
-        <v>30</v>
-      </c>
-      <c r="C6" s="58">
-        <f>i!H6/i!F6</f>
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <v>325</v>
-      </c>
-      <c r="E6" s="27">
-        <f t="shared" si="2"/>
-        <v>975</v>
-      </c>
-      <c r="F6" s="27">
-        <f t="shared" si="0"/>
-        <v>975</v>
-      </c>
-      <c r="G6" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="H6" s="27">
-        <f t="shared" si="1"/>
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="str">
-        <f>i!A7</f>
-        <v>V5</v>
-      </c>
-      <c r="B7" s="4">
-        <f>i!F7</f>
-        <v>25</v>
-      </c>
-      <c r="C7" s="58">
-        <f>i!H7/i!F7</f>
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <v>325</v>
-      </c>
-      <c r="E7" s="27">
-        <f t="shared" si="2"/>
-        <v>812.5</v>
-      </c>
-      <c r="F7" s="28">
-        <f t="shared" si="0"/>
-        <v>812.5</v>
-      </c>
-      <c r="G7" s="26">
-        <v>1.2</v>
-      </c>
-      <c r="H7" s="27">
-        <f t="shared" si="1"/>
-        <v>975</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="str">
-        <f>i!A8</f>
+        <v>0.72168783648703216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="7">
+        <v>2</v>
+      </c>
+      <c r="C8" s="7">
+        <v>22</v>
+      </c>
+      <c r="D8" s="7">
+        <v>230</v>
+      </c>
+      <c r="E8" s="34" t="str">
+        <f>B8&amp;"PL-"&amp;C8&amp;"x"&amp;D8</f>
+        <v>2PL-22x230</v>
+      </c>
+      <c r="F8" s="34">
+        <f>B8*C8*D8/100</f>
+        <v>101.2</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="34">
+        <f>F8-2*C8*24/100</f>
+        <v>90.64</v>
+      </c>
+      <c r="I8" s="33">
+        <f t="shared" ref="I8" si="9">D8*(B8*C8)^3/12/10000</f>
+        <v>163.26933333333332</v>
+      </c>
+      <c r="J8" s="30">
+        <f t="shared" ref="J8" si="10">SQRT(I8/F8)</f>
+        <v>1.2701705922171767</v>
+      </c>
+      <c r="L8" s="16" t="str">
+        <f t="shared" ref="L8" si="11">A8</f>
         <v>V11</v>
       </c>
-      <c r="B8" s="4">
-        <f>i!F8</f>
+      <c r="M8" s="16" t="str">
+        <f t="shared" ref="M8" si="12">E8</f>
+        <v>2PL-22x230</v>
+      </c>
+      <c r="N8" s="16">
+        <f t="shared" ref="N8" si="13">F8</f>
         <v>101.2</v>
       </c>
-      <c r="C8" s="58">
-        <f>i!H8/i!F8</f>
-        <v>0.89565217391304341</v>
-      </c>
-      <c r="D8" s="4">
-        <v>440</v>
-      </c>
-      <c r="E8" s="27">
-        <f t="shared" si="2"/>
-        <v>3988.16</v>
-      </c>
-      <c r="F8" s="27">
-        <f t="shared" si="0"/>
-        <v>4452.8</v>
-      </c>
-      <c r="G8" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="H8" s="27">
-        <f t="shared" si="1"/>
-        <v>5343.36</v>
+      <c r="O8" s="16" t="str">
+        <f t="shared" ref="O8" si="14">G8</f>
+        <v>2x13-M22(S10T)</v>
+      </c>
+      <c r="P8" s="16" t="str">
+        <f t="shared" si="4"/>
+        <v>90.64 (89.6%)</v>
+      </c>
+      <c r="Q8" s="55">
+        <f t="shared" ref="Q8" si="15">J8</f>
+        <v>1.2701705922171767</v>
       </c>
     </row>
   </sheetData>
@@ -2937,8 +3201,273 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B37F469-DE1B-4FCA-B9FC-D097C1860EA9}">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="66" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="str">
+        <f>section!A2</f>
+        <v>V0</v>
+      </c>
+      <c r="B2" s="4">
+        <f>section!F2</f>
+        <v>133.5</v>
+      </c>
+      <c r="C2" s="57">
+        <f>section!H2/section!F2</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>325</v>
+      </c>
+      <c r="E2" s="26">
+        <f>B2*100*C2*D2/1000</f>
+        <v>4338.75</v>
+      </c>
+      <c r="F2" s="26">
+        <f t="shared" ref="F2:F8" si="0">B2*100*D2/1000</f>
+        <v>4338.75</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="H2" s="26">
+        <f t="shared" ref="H2:H8" si="1">G2*F2</f>
+        <v>5206.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="str">
+        <f>section!A3</f>
+        <v>V1</v>
+      </c>
+      <c r="B3" s="4">
+        <f>section!F3</f>
+        <v>91.43</v>
+      </c>
+      <c r="C3" s="57">
+        <f>section!H3/section!F3</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
+        <v>325</v>
+      </c>
+      <c r="E3" s="26">
+        <f t="shared" ref="E3:E8" si="2">B3*100*C3*D3/1000</f>
+        <v>2971.4749999999999</v>
+      </c>
+      <c r="F3" s="26">
+        <f t="shared" si="0"/>
+        <v>2971.4749999999999</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="H3" s="26">
+        <f t="shared" si="1"/>
+        <v>3565.77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="str">
+        <f>section!A4</f>
+        <v>V2</v>
+      </c>
+      <c r="B4" s="4">
+        <f>section!F4</f>
+        <v>66</v>
+      </c>
+      <c r="C4" s="57">
+        <f>section!H4/section!F4</f>
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>325</v>
+      </c>
+      <c r="E4" s="26">
+        <f t="shared" si="2"/>
+        <v>2145</v>
+      </c>
+      <c r="F4" s="26">
+        <f t="shared" si="0"/>
+        <v>2145</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="H4" s="26">
+        <f t="shared" si="1"/>
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="str">
+        <f>section!A5</f>
+        <v>V3</v>
+      </c>
+      <c r="B5" s="4">
+        <f>section!F5</f>
+        <v>50</v>
+      </c>
+      <c r="C5" s="57">
+        <f>section!H5/section!F5</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
+        <v>325</v>
+      </c>
+      <c r="E5" s="26">
+        <f t="shared" si="2"/>
+        <v>1625</v>
+      </c>
+      <c r="F5" s="26">
+        <f t="shared" si="0"/>
+        <v>1625</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="H5" s="26">
+        <f t="shared" si="1"/>
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="str">
+        <f>section!A6</f>
+        <v>V4</v>
+      </c>
+      <c r="B6" s="4">
+        <f>section!F6</f>
+        <v>30</v>
+      </c>
+      <c r="C6" s="57">
+        <f>section!H6/section!F6</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
+        <v>325</v>
+      </c>
+      <c r="E6" s="26">
+        <f t="shared" si="2"/>
+        <v>975</v>
+      </c>
+      <c r="F6" s="26">
+        <f t="shared" si="0"/>
+        <v>975</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="H6" s="26">
+        <f t="shared" si="1"/>
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="str">
+        <f>section!A7</f>
+        <v>V5</v>
+      </c>
+      <c r="B7" s="4">
+        <f>section!F7</f>
+        <v>25</v>
+      </c>
+      <c r="C7" s="57">
+        <f>section!H7/section!F7</f>
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>325</v>
+      </c>
+      <c r="E7" s="26">
+        <f t="shared" si="2"/>
+        <v>812.5</v>
+      </c>
+      <c r="F7" s="27">
+        <f t="shared" si="0"/>
+        <v>812.5</v>
+      </c>
+      <c r="G7" s="25">
+        <v>1.2</v>
+      </c>
+      <c r="H7" s="26">
+        <f t="shared" si="1"/>
+        <v>975</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="str">
+        <f>section!A8</f>
+        <v>V11</v>
+      </c>
+      <c r="B8" s="4">
+        <f>section!F8</f>
+        <v>101.2</v>
+      </c>
+      <c r="C8" s="57">
+        <f>section!H8/section!F8</f>
+        <v>0.89565217391304341</v>
+      </c>
+      <c r="D8" s="4">
+        <v>440</v>
+      </c>
+      <c r="E8" s="26">
+        <f t="shared" si="2"/>
+        <v>3988.16</v>
+      </c>
+      <c r="F8" s="26">
+        <f t="shared" si="0"/>
+        <v>4452.8</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="H8" s="26">
+        <f t="shared" si="1"/>
+        <v>5343.36</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AL997"/>
@@ -2955,13 +3484,13 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>3</v>
@@ -3001,35 +3530,35 @@
       <c r="AE1" s="1"/>
     </row>
     <row r="2" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="str">
+      <c r="A2" s="28" t="str">
         <f>Nd!A2</f>
         <v>V0</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="26">
         <f>Nd!E2</f>
         <v>4338.75</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="11">
+        <v>50</v>
+      </c>
+      <c r="E2" s="10">
         <v>2</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="28">
         <f>1.5*E2*VLOOKUP(C2&amp;D2,bolt_qa!C:D,2,FALSE)</f>
         <v>171</v>
       </c>
       <c r="G2" s="4">
         <v>26</v>
       </c>
-      <c r="H2" s="29">
+      <c r="H2" s="28">
         <f t="shared" ref="H2:H4" si="0">F2*G2</f>
         <v>4446</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="29">
         <f t="shared" ref="I2:I4" si="1">B2/H2</f>
         <v>0.97587719298245612</v>
       </c>
@@ -3060,35 +3589,35 @@
       <c r="AE2" s="1"/>
     </row>
     <row r="3" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="str">
+      <c r="A3" s="28" t="str">
         <f>Nd!A3</f>
         <v>V1</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="26">
         <f>Nd!E3</f>
         <v>2971.4749999999999</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="11">
+        <v>53</v>
+      </c>
+      <c r="E3" s="10">
         <v>2</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="28">
         <f>1.5*E3*VLOOKUP(C3&amp;D3,bolt_qa!C:D,2,FALSE)</f>
         <v>141.30000000000001</v>
       </c>
       <c r="G3" s="4">
         <v>24</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="28">
         <f t="shared" si="0"/>
         <v>3391.2000000000003</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="29">
         <f t="shared" si="1"/>
         <v>0.87623112762443967</v>
       </c>
@@ -3119,35 +3648,35 @@
       <c r="AE3" s="1"/>
     </row>
     <row r="4" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="str">
+      <c r="A4" s="28" t="str">
         <f>Nd!A4</f>
         <v>V2</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <f>Nd!E4</f>
         <v>2145</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="11">
+        <v>53</v>
+      </c>
+      <c r="E4" s="10">
         <v>2</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="28">
         <f>1.5*E4*VLOOKUP(C4&amp;D4,bolt_qa!C:D,2,FALSE)</f>
         <v>141.30000000000001</v>
       </c>
       <c r="G4" s="4">
         <v>22</v>
       </c>
-      <c r="H4" s="29">
+      <c r="H4" s="28">
         <f t="shared" si="0"/>
         <v>3108.6000000000004</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="29">
         <f t="shared" si="1"/>
         <v>0.69002123142250527</v>
       </c>
@@ -3178,35 +3707,35 @@
       <c r="AE4" s="1"/>
     </row>
     <row r="5" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="str">
+      <c r="A5" s="28" t="str">
         <f>Nd!A5</f>
         <v>V3</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <f>Nd!E5</f>
         <v>1625</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="11">
+        <v>53</v>
+      </c>
+      <c r="E5" s="10">
         <v>2</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="28">
         <f>1.5*E5*VLOOKUP(C5&amp;D5,bolt_qa!C:D,2,FALSE)</f>
         <v>141.30000000000001</v>
       </c>
       <c r="G5" s="4">
         <v>20</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="28">
         <f t="shared" ref="H5" si="3">F5*G5</f>
         <v>2826</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="29">
         <f t="shared" ref="I5" si="4">B5/H5</f>
         <v>0.5750176928520877</v>
       </c>
@@ -3237,35 +3766,35 @@
       <c r="AE5" s="1"/>
     </row>
     <row r="6" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="str">
+      <c r="A6" s="28" t="str">
         <f>Nd!A6</f>
         <v>V4</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <f>Nd!E6</f>
         <v>975</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="11">
+        <v>50</v>
+      </c>
+      <c r="E6" s="10">
         <v>1</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="28">
         <f>1.5*E6*VLOOKUP(C6&amp;D6,bolt_qa!C:D,2,FALSE)</f>
         <v>85.5</v>
       </c>
       <c r="G6" s="4">
         <v>12</v>
       </c>
-      <c r="H6" s="29">
+      <c r="H6" s="28">
         <f>F6*G6</f>
         <v>1026</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="29">
         <f>B6/H6</f>
         <v>0.95029239766081874</v>
       </c>
@@ -3296,35 +3825,35 @@
       <c r="AE6" s="1"/>
     </row>
     <row r="7" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="str">
+      <c r="A7" s="28" t="str">
         <f>Nd!A7</f>
         <v>V5</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <f>Nd!E7</f>
         <v>812.5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="11">
+        <v>50</v>
+      </c>
+      <c r="E7" s="10">
         <v>1</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="28">
         <f>1.5*E7*VLOOKUP(C7&amp;D7,bolt_qa!C:D,2,FALSE)</f>
         <v>85.5</v>
       </c>
       <c r="G7" s="4">
         <v>10</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="28">
         <f>F7*G7</f>
         <v>855</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="29">
         <f>B7/H7</f>
         <v>0.95029239766081874</v>
       </c>
@@ -3362,35 +3891,35 @@
       <c r="AL7" s="1"/>
     </row>
     <row r="8" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="str">
+      <c r="A8" s="28" t="str">
         <f>Nd!A8</f>
         <v>V11</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <f>Nd!E8</f>
         <v>3988.16</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="11">
+        <v>50</v>
+      </c>
+      <c r="E8" s="10">
         <v>2</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="28">
         <f>1.5*E8*VLOOKUP(C8&amp;D8,bolt_qa!C:D,2,FALSE)</f>
         <v>171</v>
       </c>
       <c r="G8" s="4">
         <v>26</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="28">
         <f>F8*G8</f>
         <v>4446</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="29">
         <f>B8/H8</f>
         <v>0.89702204228520011</v>
       </c>
@@ -3760,17 +4289,17 @@
     </row>
     <row r="23" spans="1:38" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="24"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="23"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="23"/>
+      <c r="J23" s="22"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="22"/>
+      <c r="L23" s="21"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -3879,16 +4408,16 @@
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
-      <c r="S41" s="12"/>
-      <c r="T41" s="12"/>
-      <c r="U41" s="12"/>
-      <c r="V41" s="12"/>
-      <c r="W41" s="12"/>
-      <c r="X41" s="12"/>
-      <c r="Y41" s="12"/>
-      <c r="Z41" s="12"/>
-      <c r="AA41" s="12"/>
-      <c r="AB41" s="12"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="11"/>
+      <c r="U41" s="11"/>
+      <c r="V41" s="11"/>
+      <c r="W41" s="11"/>
+      <c r="X41" s="11"/>
+      <c r="Y41" s="11"/>
+      <c r="Z41" s="11"/>
+      <c r="AA41" s="11"/>
+      <c r="AB41" s="11"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
@@ -41714,10 +42243,10 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="J2:J8">
-    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="NG">
+    <cfRule type="containsText" dxfId="14" priority="4" operator="containsText" text="NG">
       <formula>NOT(ISERROR(SEARCH("NG",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41726,250 +42255,253 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA597959-495A-4C93-B376-8945B8AEB42D}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="str">
+      <c r="A2" s="28" t="str">
         <f>Nd!A2</f>
         <v>V0</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="26">
         <f>Nd!E2</f>
         <v>4338.75</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>25</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>600</v>
       </c>
-      <c r="E2" s="31">
+      <c r="E2" s="30">
         <f t="shared" ref="E2:E8" si="0">(D2-2*24)*C2/100</f>
         <v>138</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>325</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <f t="shared" ref="G2:G7" si="1">E2*100*F2/1000</f>
         <v>4485</v>
       </c>
-      <c r="H2" s="8" t="str">
+      <c r="H2" s="7" t="str">
         <f t="shared" ref="H2:H7" si="2">IF(G2&gt;B2, "OK", "NG")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="str">
+      <c r="A3" s="28" t="str">
         <f>Nd!A3</f>
         <v>V1</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="26">
         <f>Nd!E3</f>
         <v>2971.4749999999999</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>19</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>600</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="30">
         <f t="shared" si="0"/>
         <v>104.88</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>325</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <f t="shared" si="1"/>
         <v>3408.6</v>
       </c>
-      <c r="H3" s="8" t="str">
+      <c r="H3" s="7" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="str">
+      <c r="A4" s="28" t="str">
         <f>Nd!A4</f>
         <v>V2</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <f>Nd!E4</f>
         <v>2145</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>16</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>500</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="30">
         <f t="shared" si="0"/>
         <v>72.319999999999993</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>325</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <f t="shared" si="1"/>
         <v>2350.3999999999996</v>
       </c>
-      <c r="H4" s="8" t="str">
+      <c r="H4" s="7" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="str">
+      <c r="A5" s="28" t="str">
         <f>Nd!A5</f>
         <v>V3</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <f>Nd!E5</f>
         <v>1625</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>16</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>400</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <f t="shared" si="0"/>
         <v>56.32</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>325</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <f t="shared" si="1"/>
         <v>1830.4</v>
       </c>
-      <c r="H5" s="8" t="str">
+      <c r="H5" s="7" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="str">
+      <c r="A6" s="28" t="str">
         <f>Nd!A6</f>
         <v>V4</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <f>Nd!E6</f>
         <v>975</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>16</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>350</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <f t="shared" si="0"/>
         <v>48.32</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>325</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <f t="shared" si="1"/>
         <v>1570.4</v>
       </c>
-      <c r="H6" s="8" t="str">
+      <c r="H6" s="7" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="str">
+      <c r="A7" s="28" t="str">
         <f>Nd!A7</f>
         <v>V5</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <f>Nd!E7</f>
         <v>812.5</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>16</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>350</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <f t="shared" si="0"/>
         <v>48.32</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>325</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <f t="shared" si="1"/>
         <v>1570.4</v>
       </c>
-      <c r="H7" s="8" t="str">
+      <c r="H7" s="7" t="str">
         <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="str">
+      <c r="A8" s="28" t="str">
         <f>Nd!A8</f>
         <v>V11</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <f>Nd!E8</f>
         <v>3988.16</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>25</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>600</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>325</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <f t="shared" ref="G8" si="3">E8*100*F8/1000</f>
         <v>4485</v>
       </c>
-      <c r="H8" s="8" t="str">
+      <c r="H8" s="7" t="str">
         <f t="shared" ref="H8" si="4">IF(G8&gt;B8, "OK", "NG")</f>
         <v>OK</v>
       </c>
@@ -41977,10 +42509,10 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="H2:H8">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="NG">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="NG">
       <formula>NOT(ISERROR(SEARCH("NG",H2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41989,8 +42521,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDBDB858-B4FF-442F-B8B9-30283354E199}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -42007,8 +42542,8 @@
       <c r="D1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="25" t="s">
-        <v>69</v>
+      <c r="E1" s="24" t="s">
+        <v>66</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>16</v>
@@ -42030,35 +42565,35 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="str">
+      <c r="A2" s="28" t="str">
         <f>Nd!A2</f>
         <v>V0</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="26">
         <f>Nd!E2</f>
         <v>4338.75</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="28">
         <f>gpl_y!C2</f>
         <v>25</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="33">
+        <v>86</v>
+      </c>
+      <c r="E2" s="32">
         <v>25</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <v>1000</v>
       </c>
-      <c r="G2" s="32">
+      <c r="G2" s="31">
         <f>F2</f>
         <v>1000</v>
       </c>
       <c r="H2" s="4">
         <v>325</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="26">
         <f t="shared" ref="I2:I7" si="0">E2*G2*H2/SQRT(3)/1000</f>
         <v>4690.9709371657091</v>
       </c>
@@ -42071,35 +42606,35 @@
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="str">
+      <c r="A3" s="28" t="str">
         <f>Nd!A3</f>
         <v>V1</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="26">
         <f>Nd!E3</f>
         <v>2971.4749999999999</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="28">
         <f>gpl_y!C3</f>
         <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="33">
+        <v>86</v>
+      </c>
+      <c r="E3" s="32">
         <v>19</v>
       </c>
       <c r="F3" s="4">
         <v>900</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="31">
         <f t="shared" ref="G3:G8" si="2">F3</f>
         <v>900</v>
       </c>
       <c r="H3" s="4">
         <v>325</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="26">
         <f t="shared" si="0"/>
         <v>3208.6241210213452</v>
       </c>
@@ -42112,36 +42647,36 @@
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="str">
+      <c r="A4" s="28" t="str">
         <f>Nd!A4</f>
         <v>V2</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <f>Nd!E4</f>
         <v>2145</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="28">
         <f>gpl_y!C4</f>
         <v>16</v>
       </c>
       <c r="D4" s="5">
         <v>12</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="32">
         <f>2*0.7*D4</f>
         <v>16.799999999999997</v>
       </c>
       <c r="F4" s="4">
         <v>750</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="31">
         <f>F4-2*D4</f>
         <v>726</v>
       </c>
       <c r="H4" s="4">
         <v>325</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="26">
         <f t="shared" si="0"/>
         <v>2288.5933730569086</v>
       </c>
@@ -42154,36 +42689,36 @@
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="str">
+      <c r="A5" s="28" t="str">
         <f>Nd!A5</f>
         <v>V3</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <f>Nd!E5</f>
         <v>1625</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="28">
         <f>gpl_y!C5</f>
         <v>16</v>
       </c>
       <c r="D5" s="5">
         <v>12</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="32">
         <f t="shared" ref="E5:E7" si="3">2*0.7*D5</f>
         <v>16.799999999999997</v>
       </c>
       <c r="F5" s="4">
         <v>550</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="31">
         <f t="shared" ref="G5:G7" si="4">F5-2*D5</f>
         <v>526</v>
       </c>
       <c r="H5" s="4">
         <v>325</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="26">
         <f t="shared" si="0"/>
         <v>1658.1268791018376</v>
       </c>
@@ -42196,36 +42731,36 @@
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="str">
+      <c r="A6" s="28" t="str">
         <f>Nd!A6</f>
         <v>V4</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <f>Nd!E6</f>
         <v>975</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="28">
         <f>gpl_y!C6</f>
         <v>16</v>
       </c>
       <c r="D6" s="5">
         <v>12</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="32">
         <f t="shared" si="3"/>
         <v>16.799999999999997</v>
       </c>
       <c r="F6" s="4">
         <v>350</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="31">
         <f t="shared" si="4"/>
         <v>326</v>
       </c>
       <c r="H6" s="4">
         <v>325</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="26">
         <f t="shared" si="0"/>
         <v>1027.6603851467662</v>
       </c>
@@ -42238,36 +42773,36 @@
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="str">
+      <c r="A7" s="28" t="str">
         <f>Nd!A7</f>
         <v>V5</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <f>Nd!E7</f>
         <v>812.5</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="28">
         <f>gpl_y!C7</f>
         <v>16</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="58">
         <v>12</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="32">
         <f t="shared" si="3"/>
         <v>16.799999999999997</v>
       </c>
       <c r="F7" s="4">
         <v>300</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="31">
         <f t="shared" si="4"/>
         <v>276</v>
       </c>
       <c r="H7" s="4">
         <v>325</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="26">
         <f t="shared" si="0"/>
         <v>870.04376165799829</v>
       </c>
@@ -42277,1673 +42812,40 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="str">
+      <c r="A8" s="28" t="str">
         <f>Nd!A8</f>
         <v>V11</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <f>Nd!E8</f>
         <v>3988.16</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="28">
         <f>gpl_y!C8</f>
         <v>25</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" s="33">
+        <v>86</v>
+      </c>
+      <c r="E8" s="32">
         <v>25</v>
       </c>
       <c r="F8" s="4">
         <v>950</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="31">
         <f t="shared" si="2"/>
         <v>950</v>
       </c>
       <c r="H8" s="4">
         <v>325</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="26">
         <f t="shared" ref="I8" si="5">E8*G8*H8/SQRT(3)/1000</f>
         <v>4456.4223903074244</v>
       </c>
       <c r="J8" s="4" t="str">
         <f t="shared" ref="J8" si="6">IF(I8&gt;B8, "OK", "NG")</f>
-        <v>OK</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="J2:J8">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",J2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",J2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EA37D1-59AC-45F3-9F15-0CF7F31796EF}">
-  <dimension ref="A1:AJ11"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:36" ht="33" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="S1" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="T1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="U1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="V1" s="1"/>
-      <c r="W1" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="X1" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y1" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z1" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA1" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB1" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC1" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD1" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE1" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="AF1" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH1" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI1" s="2"/>
-      <c r="AJ1" s="2"/>
-    </row>
-    <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="60" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="34">
-        <f>_xlfn.XLOOKUP(B2,Nd!A:A,Nd!E:E)</f>
-        <v>3988.16</v>
-      </c>
-      <c r="D2" s="14">
-        <v>30</v>
-      </c>
-      <c r="E2" s="34">
-        <f t="shared" ref="E2" si="0">COS(D2/180*PI())*C2</f>
-        <v>3453.8478743569472</v>
-      </c>
-      <c r="F2" s="9">
-        <v>600</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I2" s="29">
-        <f>1.5*P2*VLOOKUP(G2&amp;H2,bolt_qa!C:D,2,FALSE)</f>
-        <v>171</v>
-      </c>
-      <c r="J2" s="35">
-        <f t="shared" ref="J2" si="1">ROUNDUP(SQRT((E2^2+F2^2)/(I2^2)),0)</f>
-        <v>21</v>
-      </c>
-      <c r="K2" s="8">
-        <v>24</v>
-      </c>
-      <c r="L2" s="8">
-        <v>3</v>
-      </c>
-      <c r="M2" s="8">
-        <v>90</v>
-      </c>
-      <c r="N2" s="8">
-        <v>12</v>
-      </c>
-      <c r="O2" s="35">
-        <f t="shared" ref="O2" si="2">(K2/L2-1)*M2+80</f>
-        <v>710</v>
-      </c>
-      <c r="P2" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="35">
-        <f t="shared" ref="Q2" si="3">N2*(O2-(K2/L2)*24)*P2</f>
-        <v>12432</v>
-      </c>
-      <c r="R2" s="8">
-        <v>325</v>
-      </c>
-      <c r="S2" s="35">
-        <f t="shared" ref="S2" si="4">Q2*R2/1000</f>
-        <v>4040.4</v>
-      </c>
-      <c r="T2" s="36">
-        <f t="shared" ref="T2" si="5">E2/S2</f>
-        <v>0.85482820373154811</v>
-      </c>
-      <c r="U2" s="8" t="str">
-        <f>IF(AND(J2&lt;=K2, T2&lt;1), "OK", "NG")</f>
-        <v>OK</v>
-      </c>
-      <c r="V2" s="1"/>
-      <c r="W2" s="16" t="str">
-        <f t="shared" ref="W2" si="6">A2</f>
-        <v>G1(ピン端)</v>
-      </c>
-      <c r="X2" s="16" t="str">
-        <f t="shared" ref="X2" si="7">B2</f>
-        <v>V11</v>
-      </c>
-      <c r="Y2" s="18">
-        <f t="shared" ref="Y2" si="8">C2</f>
-        <v>3988.16</v>
-      </c>
-      <c r="Z2" s="18">
-        <f t="shared" ref="Z2" si="9">E2</f>
-        <v>3453.8478743569472</v>
-      </c>
-      <c r="AA2" s="18">
-        <f t="shared" ref="AA2" si="10">F2</f>
-        <v>600</v>
-      </c>
-      <c r="AB2" s="16">
-        <f t="shared" ref="AB2" si="11">I2</f>
-        <v>171</v>
-      </c>
-      <c r="AC2" s="16">
-        <f t="shared" ref="AC2" si="12">J2</f>
-        <v>21</v>
-      </c>
-      <c r="AD2" s="16">
-        <f t="shared" ref="AD2" si="13">K2</f>
-        <v>24</v>
-      </c>
-      <c r="AE2" s="8">
-        <f t="shared" ref="AE2" si="14">N2</f>
-        <v>12</v>
-      </c>
-      <c r="AF2" s="17">
-        <f t="shared" ref="AF2" si="15">Q2</f>
-        <v>12432</v>
-      </c>
-      <c r="AG2" s="17">
-        <f t="shared" ref="AG2" si="16">S2</f>
-        <v>4040.4</v>
-      </c>
-      <c r="AH2" s="17" t="str">
-        <f t="shared" ref="AH2" si="17">U2</f>
-        <v>OK</v>
-      </c>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-    </row>
-    <row r="3" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="60" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="34">
-        <f>_xlfn.XLOOKUP(B3,Nd!A:A,Nd!E:E)</f>
-        <v>3988.16</v>
-      </c>
-      <c r="D3" s="14">
-        <v>30</v>
-      </c>
-      <c r="E3" s="34">
-        <f t="shared" ref="E3" si="18">COS(D3/180*PI())*C3</f>
-        <v>3453.8478743569472</v>
-      </c>
-      <c r="F3" s="9">
-        <v>600</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="29">
-        <f>1.5*P3*VLOOKUP(G3&amp;H3,bolt_qa!C:D,2,FALSE)</f>
-        <v>171</v>
-      </c>
-      <c r="J3" s="35">
-        <f t="shared" ref="J3" si="19">ROUNDUP(SQRT((E3^2+F3^2)/(I3^2)),0)</f>
-        <v>21</v>
-      </c>
-      <c r="K3" s="8">
-        <v>22</v>
-      </c>
-      <c r="L3" s="8">
-        <v>2</v>
-      </c>
-      <c r="M3" s="8">
-        <v>60</v>
-      </c>
-      <c r="N3" s="8">
-        <v>16</v>
-      </c>
-      <c r="O3" s="35">
-        <f t="shared" ref="O3" si="20">(K3/L3-1)*M3+80</f>
-        <v>680</v>
-      </c>
-      <c r="P3" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="35">
-        <f t="shared" ref="Q3" si="21">N3*(O3-(K3/L3)*24)*P3</f>
-        <v>13312</v>
-      </c>
-      <c r="R3" s="8">
-        <v>325</v>
-      </c>
-      <c r="S3" s="35">
-        <f t="shared" ref="S3" si="22">Q3*R3/1000</f>
-        <v>4326.3999999999996</v>
-      </c>
-      <c r="T3" s="36">
-        <f t="shared" ref="T3" si="23">E3/S3</f>
-        <v>0.7983191277637175</v>
-      </c>
-      <c r="U3" s="8" t="str">
-        <f t="shared" ref="U3:U10" si="24">IF(AND(J3&lt;=K3, T3&lt;1), "OK", "NG")</f>
-        <v>OK</v>
-      </c>
-      <c r="V3" s="1"/>
-      <c r="W3" s="16" t="str">
-        <f t="shared" ref="W3" si="25">A3</f>
-        <v>G1A(ピン端)</v>
-      </c>
-      <c r="X3" s="16" t="str">
-        <f t="shared" ref="X3" si="26">B3</f>
-        <v>V11</v>
-      </c>
-      <c r="Y3" s="18">
-        <f t="shared" ref="Y3" si="27">C3</f>
-        <v>3988.16</v>
-      </c>
-      <c r="Z3" s="18">
-        <f t="shared" ref="Z3" si="28">E3</f>
-        <v>3453.8478743569472</v>
-      </c>
-      <c r="AA3" s="18">
-        <f t="shared" ref="AA3" si="29">F3</f>
-        <v>600</v>
-      </c>
-      <c r="AB3" s="16">
-        <f t="shared" ref="AB3" si="30">I3</f>
-        <v>171</v>
-      </c>
-      <c r="AC3" s="16">
-        <f t="shared" ref="AC3" si="31">J3</f>
-        <v>21</v>
-      </c>
-      <c r="AD3" s="16">
-        <f t="shared" ref="AD3" si="32">K3</f>
-        <v>22</v>
-      </c>
-      <c r="AE3" s="8">
-        <f t="shared" ref="AE3" si="33">N3</f>
-        <v>16</v>
-      </c>
-      <c r="AF3" s="17">
-        <f t="shared" ref="AF3" si="34">Q3</f>
-        <v>13312</v>
-      </c>
-      <c r="AG3" s="17">
-        <f t="shared" ref="AG3" si="35">S3</f>
-        <v>4326.3999999999996</v>
-      </c>
-      <c r="AH3" s="17" t="str">
-        <f t="shared" ref="AH3" si="36">U3</f>
-        <v>OK</v>
-      </c>
-      <c r="AI3" s="2"/>
-      <c r="AJ3" s="2"/>
-    </row>
-    <row r="4" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="60" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="34">
-        <f>_xlfn.XLOOKUP(B4,Nd!A:A,Nd!E:E)</f>
-        <v>2971.4749999999999</v>
-      </c>
-      <c r="D4" s="14">
-        <v>30</v>
-      </c>
-      <c r="E4" s="34">
-        <f t="shared" ref="E4:E6" si="37">COS(D4/180*PI())*C4</f>
-        <v>2573.3728367103649</v>
-      </c>
-      <c r="F4" s="9">
-        <v>600</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" s="29">
-        <f>1.5*P4*VLOOKUP(G4&amp;H4,bolt_qa!C:D,2,FALSE)</f>
-        <v>171</v>
-      </c>
-      <c r="J4" s="35">
-        <f t="shared" ref="J4:J6" si="38">ROUNDUP(SQRT((E4^2+F4^2)/(I4^2)),0)</f>
-        <v>16</v>
-      </c>
-      <c r="K4" s="8">
-        <v>24</v>
-      </c>
-      <c r="L4" s="8">
-        <v>3</v>
-      </c>
-      <c r="M4" s="8">
-        <v>90</v>
-      </c>
-      <c r="N4" s="8">
-        <v>12</v>
-      </c>
-      <c r="O4" s="35">
-        <f t="shared" ref="O4:O6" si="39">(K4/L4-1)*M4+80</f>
-        <v>710</v>
-      </c>
-      <c r="P4" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="35">
-        <f t="shared" ref="Q4:Q6" si="40">N4*(O4-(K4/L4)*24)*P4</f>
-        <v>12432</v>
-      </c>
-      <c r="R4" s="8">
-        <v>325</v>
-      </c>
-      <c r="S4" s="35">
-        <f t="shared" ref="S4:S6" si="41">Q4*R4/1000</f>
-        <v>4040.4</v>
-      </c>
-      <c r="T4" s="36">
-        <f t="shared" ref="T4:T6" si="42">E4/S4</f>
-        <v>0.63691041399622927</v>
-      </c>
-      <c r="U4" s="8" t="str">
-        <f t="shared" si="24"/>
-        <v>OK</v>
-      </c>
-      <c r="V4" s="1"/>
-      <c r="W4" s="16" t="str">
-        <f t="shared" ref="W4:W6" si="43">A4</f>
-        <v>G89MB</v>
-      </c>
-      <c r="X4" s="16" t="str">
-        <f t="shared" ref="X4:X6" si="44">B4</f>
-        <v>V1</v>
-      </c>
-      <c r="Y4" s="18">
-        <f t="shared" ref="Y4:Y6" si="45">C4</f>
-        <v>2971.4749999999999</v>
-      </c>
-      <c r="Z4" s="18">
-        <f t="shared" ref="Z4:Z6" si="46">E4</f>
-        <v>2573.3728367103649</v>
-      </c>
-      <c r="AA4" s="18">
-        <f t="shared" ref="AA4:AA6" si="47">F4</f>
-        <v>600</v>
-      </c>
-      <c r="AB4" s="16">
-        <f t="shared" ref="AB4:AB6" si="48">I4</f>
-        <v>171</v>
-      </c>
-      <c r="AC4" s="16">
-        <f t="shared" ref="AC4:AC6" si="49">J4</f>
-        <v>16</v>
-      </c>
-      <c r="AD4" s="16">
-        <f t="shared" ref="AD4:AD6" si="50">K4</f>
-        <v>24</v>
-      </c>
-      <c r="AE4" s="8">
-        <f t="shared" ref="AE4:AE6" si="51">N4</f>
-        <v>12</v>
-      </c>
-      <c r="AF4" s="17">
-        <f t="shared" ref="AF4:AF6" si="52">Q4</f>
-        <v>12432</v>
-      </c>
-      <c r="AG4" s="17">
-        <f t="shared" ref="AG4:AG6" si="53">S4</f>
-        <v>4040.4</v>
-      </c>
-      <c r="AH4" s="17" t="str">
-        <f t="shared" ref="AH4:AH6" si="54">U4</f>
-        <v>OK</v>
-      </c>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-    </row>
-    <row r="5" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="60" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="34">
-        <f>_xlfn.XLOOKUP(B5,Nd!A:A,Nd!E:E)</f>
-        <v>4338.75</v>
-      </c>
-      <c r="D5" s="14">
-        <v>30</v>
-      </c>
-      <c r="E5" s="34">
-        <f t="shared" si="37"/>
-        <v>3757.4677206697334</v>
-      </c>
-      <c r="F5" s="9">
-        <v>600</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="29">
-        <f>1.5*P5*VLOOKUP(G5&amp;H5,bolt_qa!C:D,2,FALSE)</f>
-        <v>171</v>
-      </c>
-      <c r="J5" s="35">
-        <f t="shared" si="38"/>
-        <v>23</v>
-      </c>
-      <c r="K5" s="8">
-        <v>24</v>
-      </c>
-      <c r="L5" s="8">
-        <v>3</v>
-      </c>
-      <c r="M5" s="8">
-        <v>90</v>
-      </c>
-      <c r="N5" s="8">
-        <v>12</v>
-      </c>
-      <c r="O5" s="35">
-        <f t="shared" si="39"/>
-        <v>710</v>
-      </c>
-      <c r="P5" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="35">
-        <f t="shared" si="40"/>
-        <v>12432</v>
-      </c>
-      <c r="R5" s="8">
-        <v>325</v>
-      </c>
-      <c r="S5" s="35">
-        <f t="shared" si="41"/>
-        <v>4040.4</v>
-      </c>
-      <c r="T5" s="36">
-        <f t="shared" si="42"/>
-        <v>0.92997419083994981</v>
-      </c>
-      <c r="U5" s="8" t="str">
-        <f>IF(AND(J5&lt;=K5, T5&lt;1), "OK", "NG")</f>
-        <v>OK</v>
-      </c>
-      <c r="V5" s="1"/>
-      <c r="W5" s="16" t="str">
-        <f t="shared" si="43"/>
-        <v>G88MB</v>
-      </c>
-      <c r="X5" s="16" t="str">
-        <f t="shared" si="44"/>
-        <v>V0</v>
-      </c>
-      <c r="Y5" s="18">
-        <f t="shared" ref="Y5" si="55">C5</f>
-        <v>4338.75</v>
-      </c>
-      <c r="Z5" s="18">
-        <f t="shared" ref="Z5" si="56">E5</f>
-        <v>3757.4677206697334</v>
-      </c>
-      <c r="AA5" s="18">
-        <f t="shared" ref="AA5" si="57">F5</f>
-        <v>600</v>
-      </c>
-      <c r="AB5" s="16">
-        <f t="shared" ref="AB5" si="58">I5</f>
-        <v>171</v>
-      </c>
-      <c r="AC5" s="16">
-        <f t="shared" ref="AC5" si="59">J5</f>
-        <v>23</v>
-      </c>
-      <c r="AD5" s="16">
-        <f t="shared" ref="AD5" si="60">K5</f>
-        <v>24</v>
-      </c>
-      <c r="AE5" s="8">
-        <f t="shared" ref="AE5" si="61">N5</f>
-        <v>12</v>
-      </c>
-      <c r="AF5" s="17">
-        <f t="shared" ref="AF5" si="62">Q5</f>
-        <v>12432</v>
-      </c>
-      <c r="AG5" s="17">
-        <f t="shared" ref="AG5" si="63">S5</f>
-        <v>4040.4</v>
-      </c>
-      <c r="AH5" s="17" t="str">
-        <f t="shared" ref="AH5" si="64">U5</f>
-        <v>OK</v>
-      </c>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2"/>
-    </row>
-    <row r="6" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B6" s="60" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="34">
-        <f>_xlfn.XLOOKUP(B6,Nd!A:A,Nd!E:E)</f>
-        <v>2971.4749999999999</v>
-      </c>
-      <c r="D6" s="14">
-        <v>30</v>
-      </c>
-      <c r="E6" s="34">
-        <f t="shared" si="37"/>
-        <v>2573.3728367103649</v>
-      </c>
-      <c r="F6" s="9">
-        <v>600</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="29">
-        <f>1.5*P6*VLOOKUP(G6&amp;H6,bolt_qa!C:D,2,FALSE)</f>
-        <v>171</v>
-      </c>
-      <c r="J6" s="35">
-        <f t="shared" si="38"/>
-        <v>16</v>
-      </c>
-      <c r="K6" s="8">
-        <v>18</v>
-      </c>
-      <c r="L6" s="8">
-        <v>2</v>
-      </c>
-      <c r="M6" s="8">
-        <v>60</v>
-      </c>
-      <c r="N6" s="8">
-        <v>12</v>
-      </c>
-      <c r="O6" s="35">
-        <f t="shared" si="39"/>
-        <v>560</v>
-      </c>
-      <c r="P6" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="35">
-        <f t="shared" si="40"/>
-        <v>8256</v>
-      </c>
-      <c r="R6" s="8">
-        <v>325</v>
-      </c>
-      <c r="S6" s="35">
-        <f t="shared" si="41"/>
-        <v>2683.2</v>
-      </c>
-      <c r="T6" s="36">
-        <f t="shared" si="42"/>
-        <v>0.95906858851757792</v>
-      </c>
-      <c r="U6" s="8" t="str">
-        <f t="shared" si="24"/>
-        <v>OK</v>
-      </c>
-      <c r="V6" s="1"/>
-      <c r="W6" s="16" t="str">
-        <f t="shared" si="43"/>
-        <v>G81MB</v>
-      </c>
-      <c r="X6" s="16" t="str">
-        <f t="shared" si="44"/>
-        <v>V1</v>
-      </c>
-      <c r="Y6" s="18">
-        <f t="shared" si="45"/>
-        <v>2971.4749999999999</v>
-      </c>
-      <c r="Z6" s="18">
-        <f t="shared" si="46"/>
-        <v>2573.3728367103649</v>
-      </c>
-      <c r="AA6" s="18">
-        <f t="shared" si="47"/>
-        <v>600</v>
-      </c>
-      <c r="AB6" s="16">
-        <f t="shared" si="48"/>
-        <v>171</v>
-      </c>
-      <c r="AC6" s="16">
-        <f t="shared" si="49"/>
-        <v>16</v>
-      </c>
-      <c r="AD6" s="16">
-        <f t="shared" si="50"/>
-        <v>18</v>
-      </c>
-      <c r="AE6" s="8">
-        <f t="shared" si="51"/>
-        <v>12</v>
-      </c>
-      <c r="AF6" s="17">
-        <f t="shared" si="52"/>
-        <v>8256</v>
-      </c>
-      <c r="AG6" s="17">
-        <f t="shared" si="53"/>
-        <v>2683.2</v>
-      </c>
-      <c r="AH6" s="17" t="str">
-        <f t="shared" si="54"/>
-        <v>OK</v>
-      </c>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2"/>
-    </row>
-    <row r="7" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="60" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="34">
-        <f>_xlfn.XLOOKUP(B7,Nd!A:A,Nd!E:E)</f>
-        <v>4338.75</v>
-      </c>
-      <c r="D7" s="14">
-        <v>30</v>
-      </c>
-      <c r="E7" s="34">
-        <f t="shared" ref="E7:E10" si="65">COS(D7/180*PI())*C7</f>
-        <v>3757.4677206697334</v>
-      </c>
-      <c r="F7" s="9">
-        <v>500</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I7" s="29">
-        <f>1.5*P7*VLOOKUP(G7&amp;H7,bolt_qa!C:D,2,FALSE)</f>
-        <v>171</v>
-      </c>
-      <c r="J7" s="35">
-        <f t="shared" ref="J7:J9" si="66">ROUNDUP(SQRT((E7^2+F7^2)/(I7^2)),0)</f>
-        <v>23</v>
-      </c>
-      <c r="K7" s="8">
-        <v>27</v>
-      </c>
-      <c r="L7" s="8">
-        <v>3</v>
-      </c>
-      <c r="M7" s="8">
-        <v>60</v>
-      </c>
-      <c r="N7" s="8">
-        <v>19</v>
-      </c>
-      <c r="O7" s="35">
-        <f t="shared" ref="O7:O10" si="67">(K7/L7-1)*M7+80</f>
-        <v>560</v>
-      </c>
-      <c r="P7" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="35">
-        <f t="shared" ref="Q7:Q10" si="68">N7*(O7-(K7/L7)*24)*P7</f>
-        <v>13072</v>
-      </c>
-      <c r="R7" s="8">
-        <v>325</v>
-      </c>
-      <c r="S7" s="35">
-        <f t="shared" ref="S7:S10" si="69">Q7*R7/1000</f>
-        <v>4248.3999999999996</v>
-      </c>
-      <c r="T7" s="36">
-        <f t="shared" ref="T7:T10" si="70">E7/S7</f>
-        <v>0.884443018705803</v>
-      </c>
-      <c r="U7" s="8" t="str">
-        <f t="shared" si="24"/>
-        <v>OK</v>
-      </c>
-      <c r="V7" s="1"/>
-      <c r="W7" s="16" t="str">
-        <f t="shared" ref="W7:Y10" si="71">A7</f>
-        <v>G80MB</v>
-      </c>
-      <c r="X7" s="16" t="str">
-        <f t="shared" si="71"/>
-        <v>V0</v>
-      </c>
-      <c r="Y7" s="18">
-        <f t="shared" si="71"/>
-        <v>4338.75</v>
-      </c>
-      <c r="Z7" s="18">
-        <f t="shared" ref="Z7:AA10" si="72">E7</f>
-        <v>3757.4677206697334</v>
-      </c>
-      <c r="AA7" s="18">
-        <f t="shared" si="72"/>
-        <v>500</v>
-      </c>
-      <c r="AB7" s="16">
-        <f t="shared" ref="AB7:AD10" si="73">I7</f>
-        <v>171</v>
-      </c>
-      <c r="AC7" s="16">
-        <f t="shared" si="73"/>
-        <v>23</v>
-      </c>
-      <c r="AD7" s="16">
-        <f t="shared" si="73"/>
-        <v>27</v>
-      </c>
-      <c r="AE7" s="8">
-        <f t="shared" ref="AE7:AE10" si="74">N7</f>
-        <v>19</v>
-      </c>
-      <c r="AF7" s="17">
-        <f t="shared" ref="AF7:AF10" si="75">Q7</f>
-        <v>13072</v>
-      </c>
-      <c r="AG7" s="17">
-        <f t="shared" ref="AG7:AG10" si="76">S7</f>
-        <v>4248.3999999999996</v>
-      </c>
-      <c r="AH7" s="17" t="str">
-        <f t="shared" ref="AH7:AH9" si="77">U7</f>
-        <v>OK</v>
-      </c>
-      <c r="AI7" s="2"/>
-      <c r="AJ7" s="2"/>
-    </row>
-    <row r="8" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="34">
-        <f>_xlfn.XLOOKUP(B8,Nd!A:A,Nd!E:E)</f>
-        <v>975</v>
-      </c>
-      <c r="D8" s="14">
-        <v>30</v>
-      </c>
-      <c r="E8" s="34">
-        <f t="shared" si="65"/>
-        <v>844.37476868982776</v>
-      </c>
-      <c r="F8" s="9">
-        <v>100</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="29">
-        <f>1.5*P8*VLOOKUP(G8&amp;H8,bolt_qa!C:D,2,FALSE)</f>
-        <v>85.5</v>
-      </c>
-      <c r="J8" s="35">
-        <f t="shared" si="66"/>
-        <v>10</v>
-      </c>
-      <c r="K8" s="8">
-        <v>10</v>
-      </c>
-      <c r="L8" s="8">
-        <v>2</v>
-      </c>
-      <c r="M8" s="8">
-        <v>60</v>
-      </c>
-      <c r="N8" s="8">
-        <v>16</v>
-      </c>
-      <c r="O8" s="35">
-        <f t="shared" si="67"/>
-        <v>320</v>
-      </c>
-      <c r="P8" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="35">
-        <f t="shared" si="68"/>
-        <v>3200</v>
-      </c>
-      <c r="R8" s="8">
-        <v>325</v>
-      </c>
-      <c r="S8" s="35">
-        <f t="shared" si="69"/>
-        <v>1040</v>
-      </c>
-      <c r="T8" s="36">
-        <f t="shared" si="70"/>
-        <v>0.81189881604791125</v>
-      </c>
-      <c r="U8" s="8" t="str">
-        <f t="shared" si="24"/>
-        <v>OK</v>
-      </c>
-      <c r="V8" s="1"/>
-      <c r="W8" s="16" t="str">
-        <f t="shared" si="71"/>
-        <v>G49MB</v>
-      </c>
-      <c r="X8" s="16" t="str">
-        <f t="shared" si="71"/>
-        <v>V4</v>
-      </c>
-      <c r="Y8" s="18">
-        <f t="shared" si="71"/>
-        <v>975</v>
-      </c>
-      <c r="Z8" s="18">
-        <f t="shared" si="72"/>
-        <v>844.37476868982776</v>
-      </c>
-      <c r="AA8" s="18">
-        <f t="shared" si="72"/>
-        <v>100</v>
-      </c>
-      <c r="AB8" s="16">
-        <f t="shared" si="73"/>
-        <v>85.5</v>
-      </c>
-      <c r="AC8" s="16">
-        <f t="shared" si="73"/>
-        <v>10</v>
-      </c>
-      <c r="AD8" s="16">
-        <f t="shared" si="73"/>
-        <v>10</v>
-      </c>
-      <c r="AE8" s="8">
-        <f t="shared" si="74"/>
-        <v>16</v>
-      </c>
-      <c r="AF8" s="17">
-        <f t="shared" si="75"/>
-        <v>3200</v>
-      </c>
-      <c r="AG8" s="17">
-        <f t="shared" si="76"/>
-        <v>1040</v>
-      </c>
-      <c r="AH8" s="17" t="str">
-        <f t="shared" si="77"/>
-        <v>OK</v>
-      </c>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2"/>
-    </row>
-    <row r="9" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="34">
-        <f>_xlfn.XLOOKUP(B9,Nd!A:A,Nd!E:E)</f>
-        <v>975</v>
-      </c>
-      <c r="D9" s="14">
-        <v>30</v>
-      </c>
-      <c r="E9" s="34">
-        <f t="shared" si="65"/>
-        <v>844.37476868982776</v>
-      </c>
-      <c r="F9" s="9">
-        <v>100</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I9" s="29">
-        <f>1.5*P9*VLOOKUP(G9&amp;H9,bolt_qa!C:D,2,FALSE)</f>
-        <v>85.5</v>
-      </c>
-      <c r="J9" s="35">
-        <f t="shared" si="66"/>
-        <v>10</v>
-      </c>
-      <c r="K9" s="8">
-        <v>10</v>
-      </c>
-      <c r="L9" s="8">
-        <v>2</v>
-      </c>
-      <c r="M9" s="8">
-        <v>60</v>
-      </c>
-      <c r="N9" s="8">
-        <v>16</v>
-      </c>
-      <c r="O9" s="35">
-        <f t="shared" si="67"/>
-        <v>320</v>
-      </c>
-      <c r="P9" s="8">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="35">
-        <f t="shared" si="68"/>
-        <v>3200</v>
-      </c>
-      <c r="R9" s="8">
-        <v>325</v>
-      </c>
-      <c r="S9" s="35">
-        <f t="shared" si="69"/>
-        <v>1040</v>
-      </c>
-      <c r="T9" s="36">
-        <f t="shared" si="70"/>
-        <v>0.81189881604791125</v>
-      </c>
-      <c r="U9" s="8" t="str">
-        <f t="shared" si="24"/>
-        <v>OK</v>
-      </c>
-      <c r="V9" s="1"/>
-      <c r="W9" s="16" t="str">
-        <f t="shared" si="71"/>
-        <v>G48B</v>
-      </c>
-      <c r="X9" s="16" t="str">
-        <f t="shared" si="71"/>
-        <v>V4</v>
-      </c>
-      <c r="Y9" s="18">
-        <f t="shared" si="71"/>
-        <v>975</v>
-      </c>
-      <c r="Z9" s="18">
-        <f t="shared" si="72"/>
-        <v>844.37476868982776</v>
-      </c>
-      <c r="AA9" s="18">
-        <f t="shared" si="72"/>
-        <v>100</v>
-      </c>
-      <c r="AB9" s="16">
-        <f t="shared" si="73"/>
-        <v>85.5</v>
-      </c>
-      <c r="AC9" s="16">
-        <f t="shared" si="73"/>
-        <v>10</v>
-      </c>
-      <c r="AD9" s="16">
-        <f t="shared" si="73"/>
-        <v>10</v>
-      </c>
-      <c r="AE9" s="8">
-        <f t="shared" si="74"/>
-        <v>16</v>
-      </c>
-      <c r="AF9" s="17">
-        <f t="shared" si="75"/>
-        <v>3200</v>
-      </c>
-      <c r="AG9" s="17">
-        <f t="shared" si="76"/>
-        <v>1040</v>
-      </c>
-      <c r="AH9" s="17" t="str">
-        <f t="shared" si="77"/>
-        <v>OK</v>
-      </c>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-    </row>
-    <row r="10" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="34">
-        <f>_xlfn.XLOOKUP(B10,Nd!A:A,Nd!E:E)</f>
-        <v>1625</v>
-      </c>
-      <c r="D10" s="14">
-        <v>30</v>
-      </c>
-      <c r="E10" s="34">
-        <f t="shared" si="65"/>
-        <v>1407.2912811497129</v>
-      </c>
-      <c r="F10" s="9">
-        <v>100</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I10" s="29">
-        <f>1.5*P10*VLOOKUP(G10&amp;H10,bolt_qa!C:D,2,FALSE)</f>
-        <v>171</v>
-      </c>
-      <c r="J10" s="35">
-        <f>ROUNDUP(SQRT((E10^2+F10^2)/(I10^2)),0)</f>
-        <v>9</v>
-      </c>
-      <c r="K10" s="8">
-        <v>10</v>
-      </c>
-      <c r="L10" s="8">
-        <v>2</v>
-      </c>
-      <c r="M10" s="8">
-        <v>60</v>
-      </c>
-      <c r="N10" s="8">
-        <v>12</v>
-      </c>
-      <c r="O10" s="35">
-        <f t="shared" si="67"/>
-        <v>320</v>
-      </c>
-      <c r="P10" s="8">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="35">
-        <f t="shared" si="68"/>
-        <v>4800</v>
-      </c>
-      <c r="R10" s="8">
-        <v>325</v>
-      </c>
-      <c r="S10" s="35">
-        <f t="shared" si="69"/>
-        <v>1560</v>
-      </c>
-      <c r="T10" s="36">
-        <f t="shared" si="70"/>
-        <v>0.90210979560879034</v>
-      </c>
-      <c r="U10" s="8" t="str">
-        <f t="shared" si="24"/>
-        <v>OK</v>
-      </c>
-      <c r="V10" s="1"/>
-      <c r="W10" s="16" t="str">
-        <f t="shared" si="71"/>
-        <v>G39MB</v>
-      </c>
-      <c r="X10" s="16" t="str">
-        <f t="shared" si="71"/>
-        <v>V3</v>
-      </c>
-      <c r="Y10" s="18">
-        <f t="shared" si="71"/>
-        <v>1625</v>
-      </c>
-      <c r="Z10" s="18">
-        <f t="shared" si="72"/>
-        <v>1407.2912811497129</v>
-      </c>
-      <c r="AA10" s="18">
-        <f t="shared" si="72"/>
-        <v>100</v>
-      </c>
-      <c r="AB10" s="16">
-        <f t="shared" si="73"/>
-        <v>171</v>
-      </c>
-      <c r="AC10" s="16">
-        <f>J10</f>
-        <v>9</v>
-      </c>
-      <c r="AD10" s="16">
-        <f t="shared" si="73"/>
-        <v>10</v>
-      </c>
-      <c r="AE10" s="8">
-        <f t="shared" si="74"/>
-        <v>12</v>
-      </c>
-      <c r="AF10" s="17">
-        <f t="shared" si="75"/>
-        <v>4800</v>
-      </c>
-      <c r="AG10" s="17">
-        <f t="shared" si="76"/>
-        <v>1560</v>
-      </c>
-      <c r="AH10" s="17" t="str">
-        <f>U10</f>
-        <v>OK</v>
-      </c>
-      <c r="AI10" s="2"/>
-      <c r="AJ10" s="2"/>
-    </row>
-    <row r="11" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="18"/>
-      <c r="Z11" s="18"/>
-      <c r="AA11" s="18"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="8"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="2"/>
-      <c r="AJ11" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="U2:U11 AH2:AH11">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",U2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",U2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13403559-017D-4C60-AD87-0E8D1C842B57}">
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:10" ht="33" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="str">
-        <f>Nd!A2</f>
-        <v>V0</v>
-      </c>
-      <c r="B2" s="34">
-        <f>Nd!H2</f>
-        <v>5206.5</v>
-      </c>
-      <c r="C2" s="35" t="str">
-        <f>bolt_y!C2</f>
-        <v>S10T</v>
-      </c>
-      <c r="D2" s="35" t="str">
-        <f>bolt_y!D2</f>
-        <v>M22</v>
-      </c>
-      <c r="E2" s="35">
-        <f>bolt_y!E2</f>
-        <v>2</v>
-      </c>
-      <c r="F2" s="29">
-        <f>1.5*E2*VLOOKUP(C2&amp;D2,bolt_qa!C:E,3,FALSE)</f>
-        <v>684</v>
-      </c>
-      <c r="G2" s="35">
-        <f>bolt_y!G2</f>
-        <v>26</v>
-      </c>
-      <c r="H2" s="35">
-        <f t="shared" ref="H2:H7" si="0">F2*G2</f>
-        <v>17784</v>
-      </c>
-      <c r="I2" s="36">
-        <f t="shared" ref="I2:I7" si="1">B2/H2</f>
-        <v>0.29276315789473684</v>
-      </c>
-      <c r="J2" s="8" t="str">
-        <f t="shared" ref="J2:J8" si="2">IF(I2&lt;1, "OK", "NG")</f>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="str">
-        <f>Nd!A3</f>
-        <v>V1</v>
-      </c>
-      <c r="B3" s="34">
-        <f>Nd!H3</f>
-        <v>3565.77</v>
-      </c>
-      <c r="C3" s="35" t="str">
-        <f>bolt_y!C3</f>
-        <v>S10T</v>
-      </c>
-      <c r="D3" s="35" t="str">
-        <f>bolt_y!D3</f>
-        <v>M20</v>
-      </c>
-      <c r="E3" s="35">
-        <f>bolt_y!E3</f>
-        <v>2</v>
-      </c>
-      <c r="F3" s="29">
-        <f>1.5*E3*VLOOKUP(C3&amp;D3,bolt_qa!C:E,3,FALSE)</f>
-        <v>564</v>
-      </c>
-      <c r="G3" s="35">
-        <f>bolt_y!G3</f>
-        <v>24</v>
-      </c>
-      <c r="H3" s="35">
-        <f t="shared" si="0"/>
-        <v>13536</v>
-      </c>
-      <c r="I3" s="36">
-        <f t="shared" si="1"/>
-        <v>0.26342863475177303</v>
-      </c>
-      <c r="J3" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="str">
-        <f>Nd!A4</f>
-        <v>V2</v>
-      </c>
-      <c r="B4" s="34">
-        <f>Nd!H4</f>
-        <v>2574</v>
-      </c>
-      <c r="C4" s="35" t="str">
-        <f>bolt_y!C4</f>
-        <v>S10T</v>
-      </c>
-      <c r="D4" s="35" t="str">
-        <f>bolt_y!D4</f>
-        <v>M20</v>
-      </c>
-      <c r="E4" s="35">
-        <f>bolt_y!E4</f>
-        <v>2</v>
-      </c>
-      <c r="F4" s="29">
-        <f>1.5*E4*VLOOKUP(C4&amp;D4,bolt_qa!C:E,3,FALSE)</f>
-        <v>564</v>
-      </c>
-      <c r="G4" s="35">
-        <f>bolt_y!G4</f>
-        <v>22</v>
-      </c>
-      <c r="H4" s="35">
-        <f t="shared" si="0"/>
-        <v>12408</v>
-      </c>
-      <c r="I4" s="36">
-        <f t="shared" si="1"/>
-        <v>0.20744680851063829</v>
-      </c>
-      <c r="J4" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="str">
-        <f>Nd!A5</f>
-        <v>V3</v>
-      </c>
-      <c r="B5" s="34">
-        <f>Nd!H5</f>
-        <v>1950</v>
-      </c>
-      <c r="C5" s="35" t="str">
-        <f>bolt_y!C5</f>
-        <v>S10T</v>
-      </c>
-      <c r="D5" s="35" t="str">
-        <f>bolt_y!D5</f>
-        <v>M20</v>
-      </c>
-      <c r="E5" s="35">
-        <f>bolt_y!E5</f>
-        <v>2</v>
-      </c>
-      <c r="F5" s="29">
-        <f>1.5*E5*VLOOKUP(C5&amp;D5,bolt_qa!C:E,3,FALSE)</f>
-        <v>564</v>
-      </c>
-      <c r="G5" s="35">
-        <f>bolt_y!G5</f>
-        <v>20</v>
-      </c>
-      <c r="H5" s="35">
-        <f t="shared" si="0"/>
-        <v>11280</v>
-      </c>
-      <c r="I5" s="36">
-        <f t="shared" si="1"/>
-        <v>0.17287234042553193</v>
-      </c>
-      <c r="J5" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="str">
-        <f>Nd!A6</f>
-        <v>V4</v>
-      </c>
-      <c r="B6" s="34">
-        <f>Nd!H6</f>
-        <v>1170</v>
-      </c>
-      <c r="C6" s="35" t="str">
-        <f>bolt_y!C6</f>
-        <v>S10T</v>
-      </c>
-      <c r="D6" s="35" t="str">
-        <f>bolt_y!D6</f>
-        <v>M22</v>
-      </c>
-      <c r="E6" s="35">
-        <f>bolt_y!E6</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="29">
-        <f>1.5*E6*VLOOKUP(C6&amp;D6,bolt_qa!C:E,3,FALSE)</f>
-        <v>342</v>
-      </c>
-      <c r="G6" s="35">
-        <f>bolt_y!G6</f>
-        <v>12</v>
-      </c>
-      <c r="H6" s="35">
-        <f t="shared" si="0"/>
-        <v>4104</v>
-      </c>
-      <c r="I6" s="36">
-        <f t="shared" si="1"/>
-        <v>0.28508771929824561</v>
-      </c>
-      <c r="J6" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="str">
-        <f>Nd!A7</f>
-        <v>V5</v>
-      </c>
-      <c r="B7" s="34">
-        <f>Nd!H7</f>
-        <v>975</v>
-      </c>
-      <c r="C7" s="35" t="str">
-        <f>bolt_y!C7</f>
-        <v>S10T</v>
-      </c>
-      <c r="D7" s="35" t="str">
-        <f>bolt_y!D7</f>
-        <v>M22</v>
-      </c>
-      <c r="E7" s="35">
-        <f>bolt_y!E7</f>
-        <v>1</v>
-      </c>
-      <c r="F7" s="29">
-        <f>1.5*E7*VLOOKUP(C7&amp;D7,bolt_qa!C:E,3,FALSE)</f>
-        <v>342</v>
-      </c>
-      <c r="G7" s="35">
-        <f>bolt_y!G7</f>
-        <v>10</v>
-      </c>
-      <c r="H7" s="35">
-        <f t="shared" si="0"/>
-        <v>3420</v>
-      </c>
-      <c r="I7" s="36">
-        <f t="shared" si="1"/>
-        <v>0.28508771929824561</v>
-      </c>
-      <c r="J7" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v>OK</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="str">
-        <f>Nd!A8</f>
-        <v>V11</v>
-      </c>
-      <c r="B8" s="34">
-        <f>Nd!H8</f>
-        <v>5343.36</v>
-      </c>
-      <c r="C8" s="35" t="str">
-        <f>bolt_y!C8</f>
-        <v>S10T</v>
-      </c>
-      <c r="D8" s="35" t="str">
-        <f>bolt_y!D8</f>
-        <v>M22</v>
-      </c>
-      <c r="E8" s="35">
-        <f>bolt_y!E8</f>
-        <v>2</v>
-      </c>
-      <c r="F8" s="29">
-        <f>1.5*E8*VLOOKUP(C8&amp;D8,bolt_qa!C:E,3,FALSE)</f>
-        <v>684</v>
-      </c>
-      <c r="G8" s="35">
-        <f>bolt_y!G8</f>
-        <v>26</v>
-      </c>
-      <c r="H8" s="35">
-        <f t="shared" ref="H8" si="3">F8*G8</f>
-        <v>17784</v>
-      </c>
-      <c r="I8" s="36">
-        <f t="shared" ref="I8" si="4">B8/H8</f>
-        <v>0.30045883940620782</v>
-      </c>
-      <c r="J8" s="8" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
@@ -43958,248 +42860,1642 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EA37D1-59AC-45F3-9F15-0CF7F31796EF}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:AJ11"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:36" ht="33" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" s="1"/>
+      <c r="W1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z1" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA1" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC1" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD1" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE1" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF1" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH1" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+    </row>
+    <row r="2" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="33">
+        <f>_xlfn.XLOOKUP(B2,Nd!A:A,Nd!E:E)</f>
+        <v>3988.16</v>
+      </c>
+      <c r="D2" s="13">
+        <v>30</v>
+      </c>
+      <c r="E2" s="33">
+        <f t="shared" ref="E2" si="0">COS(D2/180*PI())*C2</f>
+        <v>3453.8478743569472</v>
+      </c>
+      <c r="F2" s="8">
+        <v>600</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="28">
+        <f>1.5*P2*VLOOKUP(G2&amp;H2,bolt_qa!C:D,2,FALSE)</f>
+        <v>171</v>
+      </c>
+      <c r="J2" s="34">
+        <f t="shared" ref="J2" si="1">ROUNDUP(SQRT((E2^2+F2^2)/(I2^2)),0)</f>
+        <v>21</v>
+      </c>
+      <c r="K2" s="7">
+        <v>24</v>
+      </c>
+      <c r="L2" s="7">
+        <v>3</v>
+      </c>
+      <c r="M2" s="7">
+        <v>90</v>
+      </c>
+      <c r="N2" s="7">
+        <v>12</v>
+      </c>
+      <c r="O2" s="34">
+        <f t="shared" ref="O2" si="2">(K2/L2-1)*M2+80</f>
+        <v>710</v>
+      </c>
+      <c r="P2" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="34">
+        <f t="shared" ref="Q2" si="3">N2*(O2-(K2/L2)*24)*P2</f>
+        <v>12432</v>
+      </c>
+      <c r="R2" s="7">
+        <v>325</v>
+      </c>
+      <c r="S2" s="34">
+        <f t="shared" ref="S2" si="4">Q2*R2/1000</f>
+        <v>4040.4</v>
+      </c>
+      <c r="T2" s="35">
+        <f t="shared" ref="T2" si="5">E2/S2</f>
+        <v>0.85482820373154811</v>
+      </c>
+      <c r="U2" s="7" t="str">
+        <f>IF(AND(J2&lt;=K2, T2&lt;1), "OK", "NG")</f>
+        <v>OK</v>
+      </c>
+      <c r="V2" s="1"/>
+      <c r="W2" s="15" t="str">
+        <f t="shared" ref="W2" si="6">A2</f>
+        <v>G1(ピン端)</v>
+      </c>
+      <c r="X2" s="15" t="str">
+        <f t="shared" ref="X2" si="7">B2</f>
+        <v>V11</v>
+      </c>
+      <c r="Y2" s="17">
+        <f t="shared" ref="Y2" si="8">C2</f>
+        <v>3988.16</v>
+      </c>
+      <c r="Z2" s="17">
+        <f t="shared" ref="Z2" si="9">E2</f>
+        <v>3453.8478743569472</v>
+      </c>
+      <c r="AA2" s="17">
+        <f t="shared" ref="AA2" si="10">F2</f>
+        <v>600</v>
+      </c>
+      <c r="AB2" s="15">
+        <f t="shared" ref="AB2" si="11">I2</f>
+        <v>171</v>
+      </c>
+      <c r="AC2" s="15">
+        <f t="shared" ref="AC2" si="12">J2</f>
+        <v>21</v>
+      </c>
+      <c r="AD2" s="15">
+        <f t="shared" ref="AD2" si="13">K2</f>
+        <v>24</v>
+      </c>
+      <c r="AE2" s="7">
+        <f t="shared" ref="AE2" si="14">N2</f>
+        <v>12</v>
+      </c>
+      <c r="AF2" s="16">
+        <f t="shared" ref="AF2" si="15">Q2</f>
+        <v>12432</v>
+      </c>
+      <c r="AG2" s="16">
+        <f t="shared" ref="AG2" si="16">S2</f>
+        <v>4040.4</v>
+      </c>
+      <c r="AH2" s="16" t="str">
+        <f t="shared" ref="AH2" si="17">U2</f>
+        <v>OK</v>
+      </c>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+    </row>
+    <row r="3" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="33">
+        <f>_xlfn.XLOOKUP(B3,Nd!A:A,Nd!E:E)</f>
+        <v>3988.16</v>
+      </c>
+      <c r="D3" s="13">
+        <v>30</v>
+      </c>
+      <c r="E3" s="33">
+        <f t="shared" ref="E3" si="18">COS(D3/180*PI())*C3</f>
+        <v>3453.8478743569472</v>
+      </c>
+      <c r="F3" s="8">
+        <v>600</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="28">
+        <f>1.5*P3*VLOOKUP(G3&amp;H3,bolt_qa!C:D,2,FALSE)</f>
+        <v>171</v>
+      </c>
+      <c r="J3" s="34">
+        <f t="shared" ref="J3" si="19">ROUNDUP(SQRT((E3^2+F3^2)/(I3^2)),0)</f>
+        <v>21</v>
+      </c>
+      <c r="K3" s="7">
+        <v>22</v>
+      </c>
+      <c r="L3" s="7">
+        <v>2</v>
+      </c>
+      <c r="M3" s="7">
+        <v>60</v>
+      </c>
+      <c r="N3" s="7">
+        <v>16</v>
+      </c>
+      <c r="O3" s="34">
+        <f t="shared" ref="O3" si="20">(K3/L3-1)*M3+80</f>
+        <v>680</v>
+      </c>
+      <c r="P3" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="34">
+        <f t="shared" ref="Q3" si="21">N3*(O3-(K3/L3)*24)*P3</f>
+        <v>13312</v>
+      </c>
+      <c r="R3" s="7">
+        <v>325</v>
+      </c>
+      <c r="S3" s="34">
+        <f t="shared" ref="S3" si="22">Q3*R3/1000</f>
+        <v>4326.3999999999996</v>
+      </c>
+      <c r="T3" s="35">
+        <f t="shared" ref="T3" si="23">E3/S3</f>
+        <v>0.7983191277637175</v>
+      </c>
+      <c r="U3" s="7" t="str">
+        <f t="shared" ref="U3:U10" si="24">IF(AND(J3&lt;=K3, T3&lt;1), "OK", "NG")</f>
+        <v>OK</v>
+      </c>
+      <c r="V3" s="1"/>
+      <c r="W3" s="15" t="str">
+        <f t="shared" ref="W3" si="25">A3</f>
+        <v>G1A(ピン端)</v>
+      </c>
+      <c r="X3" s="15" t="str">
+        <f t="shared" ref="X3" si="26">B3</f>
+        <v>V11</v>
+      </c>
+      <c r="Y3" s="17">
+        <f t="shared" ref="Y3" si="27">C3</f>
+        <v>3988.16</v>
+      </c>
+      <c r="Z3" s="17">
+        <f t="shared" ref="Z3" si="28">E3</f>
+        <v>3453.8478743569472</v>
+      </c>
+      <c r="AA3" s="17">
+        <f t="shared" ref="AA3" si="29">F3</f>
+        <v>600</v>
+      </c>
+      <c r="AB3" s="15">
+        <f t="shared" ref="AB3" si="30">I3</f>
+        <v>171</v>
+      </c>
+      <c r="AC3" s="15">
+        <f t="shared" ref="AC3" si="31">J3</f>
+        <v>21</v>
+      </c>
+      <c r="AD3" s="15">
+        <f t="shared" ref="AD3" si="32">K3</f>
+        <v>22</v>
+      </c>
+      <c r="AE3" s="7">
+        <f t="shared" ref="AE3" si="33">N3</f>
+        <v>16</v>
+      </c>
+      <c r="AF3" s="16">
+        <f t="shared" ref="AF3" si="34">Q3</f>
+        <v>13312</v>
+      </c>
+      <c r="AG3" s="16">
+        <f t="shared" ref="AG3" si="35">S3</f>
+        <v>4326.3999999999996</v>
+      </c>
+      <c r="AH3" s="16" t="str">
+        <f t="shared" ref="AH3" si="36">U3</f>
+        <v>OK</v>
+      </c>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="2"/>
+    </row>
+    <row r="4" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="33">
+        <f>_xlfn.XLOOKUP(B4,Nd!A:A,Nd!E:E)</f>
+        <v>2971.4749999999999</v>
+      </c>
+      <c r="D4" s="13">
+        <v>30</v>
+      </c>
+      <c r="E4" s="33">
+        <f t="shared" ref="E4:E6" si="37">COS(D4/180*PI())*C4</f>
+        <v>2573.3728367103649</v>
+      </c>
+      <c r="F4" s="8">
+        <v>600</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="28">
+        <f>1.5*P4*VLOOKUP(G4&amp;H4,bolt_qa!C:D,2,FALSE)</f>
+        <v>171</v>
+      </c>
+      <c r="J4" s="34">
+        <f t="shared" ref="J4:J6" si="38">ROUNDUP(SQRT((E4^2+F4^2)/(I4^2)),0)</f>
+        <v>16</v>
+      </c>
+      <c r="K4" s="7">
+        <v>24</v>
+      </c>
+      <c r="L4" s="7">
+        <v>3</v>
+      </c>
+      <c r="M4" s="7">
+        <v>90</v>
+      </c>
+      <c r="N4" s="7">
+        <v>12</v>
+      </c>
+      <c r="O4" s="34">
+        <f t="shared" ref="O4:O6" si="39">(K4/L4-1)*M4+80</f>
+        <v>710</v>
+      </c>
+      <c r="P4" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="34">
+        <f t="shared" ref="Q4:Q6" si="40">N4*(O4-(K4/L4)*24)*P4</f>
+        <v>12432</v>
+      </c>
+      <c r="R4" s="7">
+        <v>325</v>
+      </c>
+      <c r="S4" s="34">
+        <f t="shared" ref="S4:S6" si="41">Q4*R4/1000</f>
+        <v>4040.4</v>
+      </c>
+      <c r="T4" s="35">
+        <f t="shared" ref="T4:T6" si="42">E4/S4</f>
+        <v>0.63691041399622927</v>
+      </c>
+      <c r="U4" s="7" t="str">
+        <f t="shared" si="24"/>
+        <v>OK</v>
+      </c>
+      <c r="V4" s="1"/>
+      <c r="W4" s="15" t="str">
+        <f t="shared" ref="W4:W6" si="43">A4</f>
+        <v>G89MB</v>
+      </c>
+      <c r="X4" s="15" t="str">
+        <f t="shared" ref="X4:X6" si="44">B4</f>
+        <v>V1</v>
+      </c>
+      <c r="Y4" s="17">
+        <f t="shared" ref="Y4:Y6" si="45">C4</f>
+        <v>2971.4749999999999</v>
+      </c>
+      <c r="Z4" s="17">
+        <f t="shared" ref="Z4:Z6" si="46">E4</f>
+        <v>2573.3728367103649</v>
+      </c>
+      <c r="AA4" s="17">
+        <f t="shared" ref="AA4:AA6" si="47">F4</f>
+        <v>600</v>
+      </c>
+      <c r="AB4" s="15">
+        <f t="shared" ref="AB4:AB6" si="48">I4</f>
+        <v>171</v>
+      </c>
+      <c r="AC4" s="15">
+        <f t="shared" ref="AC4:AC6" si="49">J4</f>
+        <v>16</v>
+      </c>
+      <c r="AD4" s="15">
+        <f t="shared" ref="AD4:AD6" si="50">K4</f>
+        <v>24</v>
+      </c>
+      <c r="AE4" s="7">
+        <f t="shared" ref="AE4:AE6" si="51">N4</f>
+        <v>12</v>
+      </c>
+      <c r="AF4" s="16">
+        <f t="shared" ref="AF4:AF6" si="52">Q4</f>
+        <v>12432</v>
+      </c>
+      <c r="AG4" s="16">
+        <f t="shared" ref="AG4:AG6" si="53">S4</f>
+        <v>4040.4</v>
+      </c>
+      <c r="AH4" s="16" t="str">
+        <f t="shared" ref="AH4:AH6" si="54">U4</f>
+        <v>OK</v>
+      </c>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+    </row>
+    <row r="5" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="33">
+        <f>_xlfn.XLOOKUP(B5,Nd!A:A,Nd!E:E)</f>
+        <v>4338.75</v>
+      </c>
+      <c r="D5" s="13">
+        <v>30</v>
+      </c>
+      <c r="E5" s="33">
+        <f t="shared" si="37"/>
+        <v>3757.4677206697334</v>
+      </c>
+      <c r="F5" s="8">
+        <v>600</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="28">
+        <f>1.5*P5*VLOOKUP(G5&amp;H5,bolt_qa!C:D,2,FALSE)</f>
+        <v>171</v>
+      </c>
+      <c r="J5" s="34">
+        <f t="shared" si="38"/>
+        <v>23</v>
+      </c>
+      <c r="K5" s="7">
+        <v>24</v>
+      </c>
+      <c r="L5" s="7">
+        <v>3</v>
+      </c>
+      <c r="M5" s="7">
+        <v>90</v>
+      </c>
+      <c r="N5" s="7">
+        <v>12</v>
+      </c>
+      <c r="O5" s="34">
+        <f t="shared" si="39"/>
+        <v>710</v>
+      </c>
+      <c r="P5" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="34">
+        <f t="shared" si="40"/>
+        <v>12432</v>
+      </c>
+      <c r="R5" s="7">
+        <v>325</v>
+      </c>
+      <c r="S5" s="34">
+        <f t="shared" si="41"/>
+        <v>4040.4</v>
+      </c>
+      <c r="T5" s="35">
+        <f t="shared" si="42"/>
+        <v>0.92997419083994981</v>
+      </c>
+      <c r="U5" s="7" t="str">
+        <f>IF(AND(J5&lt;=K5, T5&lt;1), "OK", "NG")</f>
+        <v>OK</v>
+      </c>
+      <c r="V5" s="1"/>
+      <c r="W5" s="15" t="str">
+        <f t="shared" si="43"/>
+        <v>G88MB</v>
+      </c>
+      <c r="X5" s="15" t="str">
+        <f t="shared" si="44"/>
+        <v>V0</v>
+      </c>
+      <c r="Y5" s="17">
+        <f t="shared" ref="Y5" si="55">C5</f>
+        <v>4338.75</v>
+      </c>
+      <c r="Z5" s="17">
+        <f t="shared" ref="Z5" si="56">E5</f>
+        <v>3757.4677206697334</v>
+      </c>
+      <c r="AA5" s="17">
+        <f t="shared" ref="AA5" si="57">F5</f>
+        <v>600</v>
+      </c>
+      <c r="AB5" s="15">
+        <f t="shared" ref="AB5" si="58">I5</f>
+        <v>171</v>
+      </c>
+      <c r="AC5" s="15">
+        <f t="shared" ref="AC5" si="59">J5</f>
+        <v>23</v>
+      </c>
+      <c r="AD5" s="15">
+        <f t="shared" ref="AD5" si="60">K5</f>
+        <v>24</v>
+      </c>
+      <c r="AE5" s="7">
+        <f t="shared" ref="AE5" si="61">N5</f>
+        <v>12</v>
+      </c>
+      <c r="AF5" s="16">
+        <f t="shared" ref="AF5" si="62">Q5</f>
+        <v>12432</v>
+      </c>
+      <c r="AG5" s="16">
+        <f t="shared" ref="AG5" si="63">S5</f>
+        <v>4040.4</v>
+      </c>
+      <c r="AH5" s="16" t="str">
+        <f t="shared" ref="AH5" si="64">U5</f>
+        <v>OK</v>
+      </c>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2"/>
+    </row>
+    <row r="6" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="33">
+        <f>_xlfn.XLOOKUP(B6,Nd!A:A,Nd!E:E)</f>
+        <v>2971.4749999999999</v>
+      </c>
+      <c r="D6" s="13">
+        <v>30</v>
+      </c>
+      <c r="E6" s="33">
+        <f t="shared" si="37"/>
+        <v>2573.3728367103649</v>
+      </c>
+      <c r="F6" s="8">
+        <v>600</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="28">
+        <f>1.5*P6*VLOOKUP(G6&amp;H6,bolt_qa!C:D,2,FALSE)</f>
+        <v>171</v>
+      </c>
+      <c r="J6" s="34">
+        <f t="shared" si="38"/>
+        <v>16</v>
+      </c>
+      <c r="K6" s="7">
+        <v>18</v>
+      </c>
+      <c r="L6" s="7">
+        <v>2</v>
+      </c>
+      <c r="M6" s="7">
+        <v>60</v>
+      </c>
+      <c r="N6" s="7">
+        <v>12</v>
+      </c>
+      <c r="O6" s="34">
+        <f t="shared" si="39"/>
+        <v>560</v>
+      </c>
+      <c r="P6" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="34">
+        <f t="shared" si="40"/>
+        <v>8256</v>
+      </c>
+      <c r="R6" s="7">
+        <v>325</v>
+      </c>
+      <c r="S6" s="34">
+        <f t="shared" si="41"/>
+        <v>2683.2</v>
+      </c>
+      <c r="T6" s="35">
+        <f t="shared" si="42"/>
+        <v>0.95906858851757792</v>
+      </c>
+      <c r="U6" s="7" t="str">
+        <f t="shared" si="24"/>
+        <v>OK</v>
+      </c>
+      <c r="V6" s="1"/>
+      <c r="W6" s="15" t="str">
+        <f t="shared" si="43"/>
+        <v>G81MB</v>
+      </c>
+      <c r="X6" s="15" t="str">
+        <f t="shared" si="44"/>
+        <v>V1</v>
+      </c>
+      <c r="Y6" s="17">
+        <f t="shared" si="45"/>
+        <v>2971.4749999999999</v>
+      </c>
+      <c r="Z6" s="17">
+        <f t="shared" si="46"/>
+        <v>2573.3728367103649</v>
+      </c>
+      <c r="AA6" s="17">
+        <f t="shared" si="47"/>
+        <v>600</v>
+      </c>
+      <c r="AB6" s="15">
+        <f t="shared" si="48"/>
+        <v>171</v>
+      </c>
+      <c r="AC6" s="15">
+        <f t="shared" si="49"/>
+        <v>16</v>
+      </c>
+      <c r="AD6" s="15">
+        <f t="shared" si="50"/>
+        <v>18</v>
+      </c>
+      <c r="AE6" s="7">
+        <f t="shared" si="51"/>
+        <v>12</v>
+      </c>
+      <c r="AF6" s="16">
+        <f t="shared" si="52"/>
+        <v>8256</v>
+      </c>
+      <c r="AG6" s="16">
+        <f t="shared" si="53"/>
+        <v>2683.2</v>
+      </c>
+      <c r="AH6" s="16" t="str">
+        <f t="shared" si="54"/>
+        <v>OK</v>
+      </c>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2"/>
+    </row>
+    <row r="7" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="33">
+        <f>_xlfn.XLOOKUP(B7,Nd!A:A,Nd!E:E)</f>
+        <v>4338.75</v>
+      </c>
+      <c r="D7" s="13">
+        <v>30</v>
+      </c>
+      <c r="E7" s="33">
+        <f t="shared" ref="E7:E10" si="65">COS(D7/180*PI())*C7</f>
+        <v>3757.4677206697334</v>
+      </c>
+      <c r="F7" s="8">
+        <v>500</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="28">
+        <f>1.5*P7*VLOOKUP(G7&amp;H7,bolt_qa!C:D,2,FALSE)</f>
+        <v>171</v>
+      </c>
+      <c r="J7" s="34">
+        <f t="shared" ref="J7:J9" si="66">ROUNDUP(SQRT((E7^2+F7^2)/(I7^2)),0)</f>
+        <v>23</v>
+      </c>
+      <c r="K7" s="7">
+        <v>27</v>
+      </c>
+      <c r="L7" s="7">
+        <v>3</v>
+      </c>
+      <c r="M7" s="7">
+        <v>60</v>
+      </c>
+      <c r="N7" s="7">
+        <v>19</v>
+      </c>
+      <c r="O7" s="34">
+        <f t="shared" ref="O7:O10" si="67">(K7/L7-1)*M7+80</f>
+        <v>560</v>
+      </c>
+      <c r="P7" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="34">
+        <f t="shared" ref="Q7:Q10" si="68">N7*(O7-(K7/L7)*24)*P7</f>
+        <v>13072</v>
+      </c>
+      <c r="R7" s="7">
+        <v>325</v>
+      </c>
+      <c r="S7" s="34">
+        <f t="shared" ref="S7:S10" si="69">Q7*R7/1000</f>
+        <v>4248.3999999999996</v>
+      </c>
+      <c r="T7" s="35">
+        <f t="shared" ref="T7:T10" si="70">E7/S7</f>
+        <v>0.884443018705803</v>
+      </c>
+      <c r="U7" s="7" t="str">
+        <f t="shared" si="24"/>
+        <v>OK</v>
+      </c>
+      <c r="V7" s="1"/>
+      <c r="W7" s="15" t="str">
+        <f t="shared" ref="W7:Y10" si="71">A7</f>
+        <v>G80MB</v>
+      </c>
+      <c r="X7" s="15" t="str">
+        <f t="shared" si="71"/>
+        <v>V0</v>
+      </c>
+      <c r="Y7" s="17">
+        <f t="shared" si="71"/>
+        <v>4338.75</v>
+      </c>
+      <c r="Z7" s="17">
+        <f t="shared" ref="Z7:AA10" si="72">E7</f>
+        <v>3757.4677206697334</v>
+      </c>
+      <c r="AA7" s="17">
+        <f t="shared" si="72"/>
+        <v>500</v>
+      </c>
+      <c r="AB7" s="15">
+        <f t="shared" ref="AB7:AD10" si="73">I7</f>
+        <v>171</v>
+      </c>
+      <c r="AC7" s="15">
+        <f t="shared" si="73"/>
+        <v>23</v>
+      </c>
+      <c r="AD7" s="15">
+        <f t="shared" si="73"/>
+        <v>27</v>
+      </c>
+      <c r="AE7" s="7">
+        <f t="shared" ref="AE7:AE10" si="74">N7</f>
+        <v>19</v>
+      </c>
+      <c r="AF7" s="16">
+        <f t="shared" ref="AF7:AF10" si="75">Q7</f>
+        <v>13072</v>
+      </c>
+      <c r="AG7" s="16">
+        <f t="shared" ref="AG7:AG10" si="76">S7</f>
+        <v>4248.3999999999996</v>
+      </c>
+      <c r="AH7" s="16" t="str">
+        <f t="shared" ref="AH7:AH9" si="77">U7</f>
+        <v>OK</v>
+      </c>
+      <c r="AI7" s="2"/>
+      <c r="AJ7" s="2"/>
+    </row>
+    <row r="8" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="33">
+        <f>_xlfn.XLOOKUP(B8,Nd!A:A,Nd!E:E)</f>
+        <v>975</v>
+      </c>
+      <c r="D8" s="13">
+        <v>30</v>
+      </c>
+      <c r="E8" s="33">
+        <f t="shared" si="65"/>
+        <v>844.37476868982776</v>
+      </c>
+      <c r="F8" s="8">
+        <v>100</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="28">
+        <f>1.5*P8*VLOOKUP(G8&amp;H8,bolt_qa!C:D,2,FALSE)</f>
+        <v>85.5</v>
+      </c>
+      <c r="J8" s="34">
+        <f t="shared" si="66"/>
+        <v>10</v>
+      </c>
+      <c r="K8" s="7">
+        <v>10</v>
+      </c>
+      <c r="L8" s="7">
+        <v>2</v>
+      </c>
+      <c r="M8" s="7">
+        <v>60</v>
+      </c>
+      <c r="N8" s="7">
+        <v>16</v>
+      </c>
+      <c r="O8" s="34">
+        <f t="shared" si="67"/>
+        <v>320</v>
+      </c>
+      <c r="P8" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="34">
+        <f t="shared" si="68"/>
+        <v>3200</v>
+      </c>
+      <c r="R8" s="7">
+        <v>325</v>
+      </c>
+      <c r="S8" s="34">
+        <f t="shared" si="69"/>
+        <v>1040</v>
+      </c>
+      <c r="T8" s="35">
+        <f t="shared" si="70"/>
+        <v>0.81189881604791125</v>
+      </c>
+      <c r="U8" s="7" t="str">
+        <f t="shared" si="24"/>
+        <v>OK</v>
+      </c>
+      <c r="V8" s="1"/>
+      <c r="W8" s="15" t="str">
+        <f t="shared" si="71"/>
+        <v>G49MB</v>
+      </c>
+      <c r="X8" s="15" t="str">
+        <f t="shared" si="71"/>
+        <v>V4</v>
+      </c>
+      <c r="Y8" s="17">
+        <f t="shared" si="71"/>
+        <v>975</v>
+      </c>
+      <c r="Z8" s="17">
+        <f t="shared" si="72"/>
+        <v>844.37476868982776</v>
+      </c>
+      <c r="AA8" s="17">
+        <f t="shared" si="72"/>
+        <v>100</v>
+      </c>
+      <c r="AB8" s="15">
+        <f t="shared" si="73"/>
+        <v>85.5</v>
+      </c>
+      <c r="AC8" s="15">
+        <f t="shared" si="73"/>
+        <v>10</v>
+      </c>
+      <c r="AD8" s="15">
+        <f t="shared" si="73"/>
+        <v>10</v>
+      </c>
+      <c r="AE8" s="7">
+        <f t="shared" si="74"/>
+        <v>16</v>
+      </c>
+      <c r="AF8" s="16">
+        <f t="shared" si="75"/>
+        <v>3200</v>
+      </c>
+      <c r="AG8" s="16">
+        <f t="shared" si="76"/>
+        <v>1040</v>
+      </c>
+      <c r="AH8" s="16" t="str">
+        <f t="shared" si="77"/>
+        <v>OK</v>
+      </c>
+      <c r="AI8" s="2"/>
+      <c r="AJ8" s="2"/>
+    </row>
+    <row r="9" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="33">
+        <f>_xlfn.XLOOKUP(B9,Nd!A:A,Nd!E:E)</f>
+        <v>975</v>
+      </c>
+      <c r="D9" s="13">
+        <v>30</v>
+      </c>
+      <c r="E9" s="33">
+        <f t="shared" si="65"/>
+        <v>844.37476868982776</v>
+      </c>
+      <c r="F9" s="8">
+        <v>100</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="28">
+        <f>1.5*P9*VLOOKUP(G9&amp;H9,bolt_qa!C:D,2,FALSE)</f>
+        <v>85.5</v>
+      </c>
+      <c r="J9" s="34">
+        <f t="shared" si="66"/>
+        <v>10</v>
+      </c>
+      <c r="K9" s="7">
+        <v>10</v>
+      </c>
+      <c r="L9" s="7">
+        <v>2</v>
+      </c>
+      <c r="M9" s="7">
+        <v>60</v>
+      </c>
+      <c r="N9" s="7">
+        <v>16</v>
+      </c>
+      <c r="O9" s="34">
+        <f t="shared" si="67"/>
+        <v>320</v>
+      </c>
+      <c r="P9" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="34">
+        <f t="shared" si="68"/>
+        <v>3200</v>
+      </c>
+      <c r="R9" s="7">
+        <v>325</v>
+      </c>
+      <c r="S9" s="34">
+        <f t="shared" si="69"/>
+        <v>1040</v>
+      </c>
+      <c r="T9" s="35">
+        <f t="shared" si="70"/>
+        <v>0.81189881604791125</v>
+      </c>
+      <c r="U9" s="7" t="str">
+        <f t="shared" si="24"/>
+        <v>OK</v>
+      </c>
+      <c r="V9" s="1"/>
+      <c r="W9" s="15" t="str">
+        <f t="shared" si="71"/>
+        <v>G48B</v>
+      </c>
+      <c r="X9" s="15" t="str">
+        <f t="shared" si="71"/>
+        <v>V4</v>
+      </c>
+      <c r="Y9" s="17">
+        <f t="shared" si="71"/>
+        <v>975</v>
+      </c>
+      <c r="Z9" s="17">
+        <f t="shared" si="72"/>
+        <v>844.37476868982776</v>
+      </c>
+      <c r="AA9" s="17">
+        <f t="shared" si="72"/>
+        <v>100</v>
+      </c>
+      <c r="AB9" s="15">
+        <f t="shared" si="73"/>
+        <v>85.5</v>
+      </c>
+      <c r="AC9" s="15">
+        <f t="shared" si="73"/>
+        <v>10</v>
+      </c>
+      <c r="AD9" s="15">
+        <f t="shared" si="73"/>
+        <v>10</v>
+      </c>
+      <c r="AE9" s="7">
+        <f t="shared" si="74"/>
+        <v>16</v>
+      </c>
+      <c r="AF9" s="16">
+        <f t="shared" si="75"/>
+        <v>3200</v>
+      </c>
+      <c r="AG9" s="16">
+        <f t="shared" si="76"/>
+        <v>1040</v>
+      </c>
+      <c r="AH9" s="16" t="str">
+        <f t="shared" si="77"/>
+        <v>OK</v>
+      </c>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+    </row>
+    <row r="10" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="33">
+        <f>_xlfn.XLOOKUP(B10,Nd!A:A,Nd!E:E)</f>
+        <v>1625</v>
+      </c>
+      <c r="D10" s="13">
+        <v>30</v>
+      </c>
+      <c r="E10" s="33">
+        <f t="shared" si="65"/>
+        <v>1407.2912811497129</v>
+      </c>
+      <c r="F10" s="8">
+        <v>100</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="28">
+        <f>1.5*P10*VLOOKUP(G10&amp;H10,bolt_qa!C:D,2,FALSE)</f>
+        <v>171</v>
+      </c>
+      <c r="J10" s="34">
+        <f>ROUNDUP(SQRT((E10^2+F10^2)/(I10^2)),0)</f>
+        <v>9</v>
+      </c>
+      <c r="K10" s="7">
+        <v>10</v>
+      </c>
+      <c r="L10" s="7">
+        <v>2</v>
+      </c>
+      <c r="M10" s="7">
+        <v>60</v>
+      </c>
+      <c r="N10" s="7">
+        <v>12</v>
+      </c>
+      <c r="O10" s="34">
+        <f t="shared" si="67"/>
+        <v>320</v>
+      </c>
+      <c r="P10" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="34">
+        <f t="shared" si="68"/>
+        <v>4800</v>
+      </c>
+      <c r="R10" s="7">
+        <v>325</v>
+      </c>
+      <c r="S10" s="34">
+        <f t="shared" si="69"/>
+        <v>1560</v>
+      </c>
+      <c r="T10" s="35">
+        <f t="shared" si="70"/>
+        <v>0.90210979560879034</v>
+      </c>
+      <c r="U10" s="7" t="str">
+        <f t="shared" si="24"/>
+        <v>OK</v>
+      </c>
+      <c r="V10" s="1"/>
+      <c r="W10" s="15" t="str">
+        <f t="shared" si="71"/>
+        <v>G39MB</v>
+      </c>
+      <c r="X10" s="15" t="str">
+        <f t="shared" si="71"/>
+        <v>V3</v>
+      </c>
+      <c r="Y10" s="17">
+        <f t="shared" si="71"/>
+        <v>1625</v>
+      </c>
+      <c r="Z10" s="17">
+        <f t="shared" si="72"/>
+        <v>1407.2912811497129</v>
+      </c>
+      <c r="AA10" s="17">
+        <f t="shared" si="72"/>
+        <v>100</v>
+      </c>
+      <c r="AB10" s="15">
+        <f t="shared" si="73"/>
+        <v>171</v>
+      </c>
+      <c r="AC10" s="15">
+        <f>J10</f>
+        <v>9</v>
+      </c>
+      <c r="AD10" s="15">
+        <f t="shared" si="73"/>
+        <v>10</v>
+      </c>
+      <c r="AE10" s="7">
+        <f t="shared" si="74"/>
+        <v>12</v>
+      </c>
+      <c r="AF10" s="16">
+        <f t="shared" si="75"/>
+        <v>4800</v>
+      </c>
+      <c r="AG10" s="16">
+        <f t="shared" si="76"/>
+        <v>1560</v>
+      </c>
+      <c r="AH10" s="16" t="str">
+        <f>U10</f>
+        <v>OK</v>
+      </c>
+      <c r="AI10" s="2"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:36" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="15"/>
+      <c r="AC11" s="15"/>
+      <c r="AD11" s="15"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="16"/>
+      <c r="AI11" s="2"/>
+      <c r="AJ11" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="U2:U11 AH2:AH11">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",U2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",U2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E73B7A-61CE-4972-8821-F3586CF779F9}">
-  <dimension ref="A1:G8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13403559-017D-4C60-AD87-0E8D1C842B57}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="7" t="s">
+      <c r="B1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="J1" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="str">
+    <row r="2" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="str">
         <f>Nd!A2</f>
         <v>V0</v>
       </c>
-      <c r="B2" s="34">
+      <c r="B2" s="33">
         <f>Nd!H2</f>
         <v>5206.5</v>
       </c>
-      <c r="C2" s="31">
-        <f>gpl_y!E2</f>
-        <v>138</v>
-      </c>
-      <c r="D2" s="8">
-        <v>490</v>
+      <c r="C2" s="34" t="str">
+        <f>bolt_y!C2</f>
+        <v>S10T</v>
+      </c>
+      <c r="D2" s="34" t="str">
+        <f>bolt_y!D2</f>
+        <v>M22</v>
       </c>
       <c r="E2" s="34">
-        <f t="shared" ref="E2:E7" si="0">D2*C2*100/1000</f>
-        <v>6762</v>
-      </c>
-      <c r="F2" s="36">
-        <f>B2/E2</f>
-        <v>0.76996450754214729</v>
-      </c>
-      <c r="G2" s="8" t="str">
-        <f t="shared" ref="G2:G8" si="1">IF(F2&lt;1, "OK", "NG")</f>
+        <f>bolt_y!E2</f>
+        <v>2</v>
+      </c>
+      <c r="F2" s="28">
+        <f>1.5*E2*VLOOKUP(C2&amp;D2,bolt_qa!C:E,3,FALSE)</f>
+        <v>684</v>
+      </c>
+      <c r="G2" s="34">
+        <f>bolt_y!G2</f>
+        <v>26</v>
+      </c>
+      <c r="H2" s="34">
+        <f t="shared" ref="H2:H7" si="0">F2*G2</f>
+        <v>17784</v>
+      </c>
+      <c r="I2" s="35">
+        <f t="shared" ref="I2:I7" si="1">B2/H2</f>
+        <v>0.29276315789473684</v>
+      </c>
+      <c r="J2" s="7" t="str">
+        <f t="shared" ref="J2:J8" si="2">IF(I2&lt;1, "OK", "NG")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="str">
+    <row r="3" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="28" t="str">
         <f>Nd!A3</f>
         <v>V1</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="33">
         <f>Nd!H3</f>
         <v>3565.77</v>
       </c>
-      <c r="C3" s="31">
-        <f>gpl_y!E3</f>
-        <v>104.88</v>
-      </c>
-      <c r="D3" s="8">
-        <v>490</v>
+      <c r="C3" s="34" t="str">
+        <f>bolt_y!C3</f>
+        <v>S10T</v>
+      </c>
+      <c r="D3" s="34" t="str">
+        <f>bolt_y!D3</f>
+        <v>M20</v>
       </c>
       <c r="E3" s="34">
+        <f>bolt_y!E3</f>
+        <v>2</v>
+      </c>
+      <c r="F3" s="28">
+        <f>1.5*E3*VLOOKUP(C3&amp;D3,bolt_qa!C:E,3,FALSE)</f>
+        <v>564</v>
+      </c>
+      <c r="G3" s="34">
+        <f>bolt_y!G3</f>
+        <v>24</v>
+      </c>
+      <c r="H3" s="34">
         <f t="shared" si="0"/>
-        <v>5139.12</v>
-      </c>
-      <c r="F3" s="36">
-        <f t="shared" ref="F3:F7" si="2">B3/E3</f>
-        <v>0.69384836314388454</v>
-      </c>
-      <c r="G3" s="8" t="str">
+        <v>13536</v>
+      </c>
+      <c r="I3" s="35">
         <f t="shared" si="1"/>
+        <v>0.26342863475177303</v>
+      </c>
+      <c r="J3" s="7" t="str">
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="str">
+    <row r="4" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="28" t="str">
         <f>Nd!A4</f>
         <v>V2</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="33">
         <f>Nd!H4</f>
         <v>2574</v>
       </c>
-      <c r="C4" s="31">
-        <f>gpl_y!E4</f>
-        <v>72.319999999999993</v>
-      </c>
-      <c r="D4" s="8">
-        <v>490</v>
+      <c r="C4" s="34" t="str">
+        <f>bolt_y!C4</f>
+        <v>S10T</v>
+      </c>
+      <c r="D4" s="34" t="str">
+        <f>bolt_y!D4</f>
+        <v>M20</v>
       </c>
       <c r="E4" s="34">
+        <f>bolt_y!E4</f>
+        <v>2</v>
+      </c>
+      <c r="F4" s="28">
+        <f>1.5*E4*VLOOKUP(C4&amp;D4,bolt_qa!C:E,3,FALSE)</f>
+        <v>564</v>
+      </c>
+      <c r="G4" s="34">
+        <f>bolt_y!G4</f>
+        <v>22</v>
+      </c>
+      <c r="H4" s="34">
         <f t="shared" si="0"/>
-        <v>3543.6799999999994</v>
-      </c>
-      <c r="F4" s="36">
+        <v>12408</v>
+      </c>
+      <c r="I4" s="35">
+        <f t="shared" si="1"/>
+        <v>0.20744680851063829</v>
+      </c>
+      <c r="J4" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0.7263635542712662</v>
-      </c>
-      <c r="G4" s="8" t="str">
-        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="str">
+    <row r="5" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="28" t="str">
         <f>Nd!A5</f>
         <v>V3</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="33">
         <f>Nd!H5</f>
         <v>1950</v>
       </c>
-      <c r="C5" s="31">
-        <f>gpl_y!E5</f>
-        <v>56.32</v>
-      </c>
-      <c r="D5" s="8">
-        <v>490</v>
+      <c r="C5" s="34" t="str">
+        <f>bolt_y!C5</f>
+        <v>S10T</v>
+      </c>
+      <c r="D5" s="34" t="str">
+        <f>bolt_y!D5</f>
+        <v>M20</v>
       </c>
       <c r="E5" s="34">
+        <f>bolt_y!E5</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="28">
+        <f>1.5*E5*VLOOKUP(C5&amp;D5,bolt_qa!C:E,3,FALSE)</f>
+        <v>564</v>
+      </c>
+      <c r="G5" s="34">
+        <f>bolt_y!G5</f>
+        <v>20</v>
+      </c>
+      <c r="H5" s="34">
         <f t="shared" si="0"/>
-        <v>2759.68</v>
-      </c>
-      <c r="F5" s="36">
+        <v>11280</v>
+      </c>
+      <c r="I5" s="35">
+        <f t="shared" si="1"/>
+        <v>0.17287234042553193</v>
+      </c>
+      <c r="J5" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0.70660366419294995</v>
-      </c>
-      <c r="G5" s="8" t="str">
-        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="str">
+    <row r="6" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="28" t="str">
         <f>Nd!A6</f>
         <v>V4</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="33">
         <f>Nd!H6</f>
         <v>1170</v>
       </c>
-      <c r="C6" s="31">
-        <f>gpl_y!E6</f>
-        <v>48.32</v>
-      </c>
-      <c r="D6" s="8">
-        <v>490</v>
+      <c r="C6" s="34" t="str">
+        <f>bolt_y!C6</f>
+        <v>S10T</v>
+      </c>
+      <c r="D6" s="34" t="str">
+        <f>bolt_y!D6</f>
+        <v>M22</v>
       </c>
       <c r="E6" s="34">
+        <f>bolt_y!E6</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="28">
+        <f>1.5*E6*VLOOKUP(C6&amp;D6,bolt_qa!C:E,3,FALSE)</f>
+        <v>342</v>
+      </c>
+      <c r="G6" s="34">
+        <f>bolt_y!G6</f>
+        <v>12</v>
+      </c>
+      <c r="H6" s="34">
         <f t="shared" si="0"/>
-        <v>2367.6799999999998</v>
-      </c>
-      <c r="F6" s="36">
+        <v>4104</v>
+      </c>
+      <c r="I6" s="35">
+        <f t="shared" si="1"/>
+        <v>0.28508771929824561</v>
+      </c>
+      <c r="J6" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0.49415461548857958</v>
-      </c>
-      <c r="G6" s="8" t="str">
-        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="str">
+    <row r="7" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="28" t="str">
         <f>Nd!A7</f>
         <v>V5</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="33">
         <f>Nd!H7</f>
         <v>975</v>
       </c>
-      <c r="C7" s="31">
-        <f>gpl_y!E7</f>
-        <v>48.32</v>
-      </c>
-      <c r="D7" s="8">
-        <v>490</v>
+      <c r="C7" s="34" t="str">
+        <f>bolt_y!C7</f>
+        <v>S10T</v>
+      </c>
+      <c r="D7" s="34" t="str">
+        <f>bolt_y!D7</f>
+        <v>M22</v>
       </c>
       <c r="E7" s="34">
+        <f>bolt_y!E7</f>
+        <v>1</v>
+      </c>
+      <c r="F7" s="28">
+        <f>1.5*E7*VLOOKUP(C7&amp;D7,bolt_qa!C:E,3,FALSE)</f>
+        <v>342</v>
+      </c>
+      <c r="G7" s="34">
+        <f>bolt_y!G7</f>
+        <v>10</v>
+      </c>
+      <c r="H7" s="34">
         <f t="shared" si="0"/>
-        <v>2367.6799999999998</v>
-      </c>
-      <c r="F7" s="36">
+        <v>3420</v>
+      </c>
+      <c r="I7" s="35">
+        <f t="shared" si="1"/>
+        <v>0.28508771929824561</v>
+      </c>
+      <c r="J7" s="7" t="str">
         <f t="shared" si="2"/>
-        <v>0.41179551290714966</v>
-      </c>
-      <c r="G7" s="8" t="str">
-        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="str">
+    <row r="8" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="28" t="str">
         <f>Nd!A8</f>
         <v>V11</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="33">
         <f>Nd!H8</f>
         <v>5343.36</v>
       </c>
-      <c r="C8" s="31">
-        <f>gpl_y!E8</f>
-        <v>138</v>
-      </c>
-      <c r="D8" s="8">
-        <v>490</v>
+      <c r="C8" s="34" t="str">
+        <f>bolt_y!C8</f>
+        <v>S10T</v>
+      </c>
+      <c r="D8" s="34" t="str">
+        <f>bolt_y!D8</f>
+        <v>M22</v>
       </c>
       <c r="E8" s="34">
-        <f t="shared" ref="E8" si="3">D8*C8*100/1000</f>
-        <v>6762</v>
-      </c>
-      <c r="F8" s="36">
-        <f t="shared" ref="F8" si="4">B8/E8</f>
-        <v>0.79020408163265299</v>
-      </c>
-      <c r="G8" s="8" t="str">
-        <f t="shared" si="1"/>
+        <f>bolt_y!E8</f>
+        <v>2</v>
+      </c>
+      <c r="F8" s="28">
+        <f>1.5*E8*VLOOKUP(C8&amp;D8,bolt_qa!C:E,3,FALSE)</f>
+        <v>684</v>
+      </c>
+      <c r="G8" s="34">
+        <f>bolt_y!G8</f>
+        <v>26</v>
+      </c>
+      <c r="H8" s="34">
+        <f t="shared" ref="H8" si="3">F8*G8</f>
+        <v>17784</v>
+      </c>
+      <c r="I8" s="35">
+        <f t="shared" ref="I8" si="4">B8/H8</f>
+        <v>0.30045883940620782</v>
+      </c>
+      <c r="J8" s="7" t="str">
+        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="G2:G8">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",G2)))</formula>
+  <conditionalFormatting sqref="J2:J8">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44207,250 +44503,246 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4716E361-ED6F-4B3B-89DF-4B973A4AF614}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E73B7A-61CE-4972-8821-F3586CF779F9}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="str">
+      <c r="A2" s="28" t="str">
         <f>Nd!A2</f>
         <v>V0</v>
       </c>
-      <c r="B2" s="34">
+      <c r="B2" s="33">
         <f>Nd!H2</f>
         <v>5206.5</v>
       </c>
-      <c r="C2" s="33">
-        <f>weld_y!E2*weld_y!G2/100</f>
-        <v>250</v>
-      </c>
-      <c r="D2" s="5">
-        <f t="shared" ref="D2:D7" si="0">490/SQRT(3)</f>
-        <v>282.90163190291662</v>
-      </c>
-      <c r="E2" s="27">
-        <f t="shared" ref="E2:E7" si="1">D2*C2*100/1000</f>
-        <v>7072.5407975729167</v>
-      </c>
-      <c r="F2" s="30">
+      <c r="C2" s="30">
+        <f>gpl_y!E2</f>
+        <v>138</v>
+      </c>
+      <c r="D2" s="7">
+        <v>490</v>
+      </c>
+      <c r="E2" s="33">
+        <f t="shared" ref="E2:E7" si="0">D2*C2*100/1000</f>
+        <v>6762</v>
+      </c>
+      <c r="F2" s="35">
         <f>B2/E2</f>
-        <v>0.73615694119243735</v>
-      </c>
-      <c r="G2" s="4" t="str">
-        <f t="shared" ref="G2:G8" si="2">IF(F2&lt;1, "OK", "NG")</f>
+        <v>0.76996450754214729</v>
+      </c>
+      <c r="G2" s="7" t="str">
+        <f t="shared" ref="G2:G8" si="1">IF(F2&lt;1, "OK", "NG")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="str">
+      <c r="A3" s="28" t="str">
         <f>Nd!A3</f>
         <v>V1</v>
       </c>
-      <c r="B3" s="34">
+      <c r="B3" s="33">
         <f>Nd!H3</f>
         <v>3565.77</v>
       </c>
-      <c r="C3" s="33">
-        <f>weld_y!E3*weld_y!G3/100</f>
-        <v>171</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="C3" s="30">
+        <f>gpl_y!E3</f>
+        <v>104.88</v>
+      </c>
+      <c r="D3" s="7">
+        <v>490</v>
+      </c>
+      <c r="E3" s="33">
         <f t="shared" si="0"/>
-        <v>282.90163190291662</v>
-      </c>
-      <c r="E3" s="27">
+        <v>5139.12</v>
+      </c>
+      <c r="F3" s="35">
+        <f t="shared" ref="F3:F7" si="2">B3/E3</f>
+        <v>0.69384836314388454</v>
+      </c>
+      <c r="G3" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>4837.6179055398752</v>
-      </c>
-      <c r="F3" s="30">
-        <f t="shared" ref="F3:F7" si="3">B3/E3</f>
-        <v>0.73709211219774129</v>
-      </c>
-      <c r="G3" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="str">
+      <c r="A4" s="28" t="str">
         <f>Nd!A4</f>
         <v>V2</v>
       </c>
-      <c r="B4" s="34">
+      <c r="B4" s="33">
         <f>Nd!H4</f>
         <v>2574</v>
       </c>
-      <c r="C4" s="33">
-        <f>weld_y!E4*weld_y!G4/100</f>
-        <v>121.96799999999998</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="C4" s="30">
+        <f>gpl_y!E4</f>
+        <v>72.319999999999993</v>
+      </c>
+      <c r="D4" s="7">
+        <v>490</v>
+      </c>
+      <c r="E4" s="33">
         <f t="shared" si="0"/>
-        <v>282.90163190291662</v>
-      </c>
-      <c r="E4" s="27">
+        <v>3543.6799999999994</v>
+      </c>
+      <c r="F4" s="35">
+        <f t="shared" si="2"/>
+        <v>0.7263635542712662</v>
+      </c>
+      <c r="G4" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>3450.4946239934925</v>
-      </c>
-      <c r="F4" s="30">
-        <f t="shared" si="3"/>
-        <v>0.74598000591026414</v>
-      </c>
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="str">
+      <c r="A5" s="28" t="str">
         <f>Nd!A5</f>
         <v>V3</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="33">
         <f>Nd!H5</f>
         <v>1950</v>
       </c>
-      <c r="C5" s="33">
-        <f>weld_y!E5*weld_y!G5/100</f>
-        <v>88.367999999999995</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C5" s="30">
+        <f>gpl_y!E5</f>
+        <v>56.32</v>
+      </c>
+      <c r="D5" s="7">
+        <v>490</v>
+      </c>
+      <c r="E5" s="33">
         <f t="shared" si="0"/>
-        <v>282.90163190291662</v>
-      </c>
-      <c r="E5" s="27">
+        <v>2759.68</v>
+      </c>
+      <c r="F5" s="35">
+        <f t="shared" si="2"/>
+        <v>0.70660366419294995</v>
+      </c>
+      <c r="G5" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>2499.9451407996935</v>
-      </c>
-      <c r="F5" s="30">
-        <f t="shared" si="3"/>
-        <v>0.78001711644609339</v>
-      </c>
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="str">
+      <c r="A6" s="28" t="str">
         <f>Nd!A6</f>
         <v>V4</v>
       </c>
-      <c r="B6" s="34">
+      <c r="B6" s="33">
         <f>Nd!H6</f>
         <v>1170</v>
       </c>
-      <c r="C6" s="33">
-        <f>weld_y!E6*weld_y!G6/100</f>
-        <v>54.767999999999994</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="C6" s="30">
+        <f>gpl_y!E6</f>
+        <v>48.32</v>
+      </c>
+      <c r="D6" s="7">
+        <v>490</v>
+      </c>
+      <c r="E6" s="33">
         <f t="shared" si="0"/>
-        <v>282.90163190291662</v>
-      </c>
-      <c r="E6" s="27">
+        <v>2367.6799999999998</v>
+      </c>
+      <c r="F6" s="35">
+        <f t="shared" si="2"/>
+        <v>0.49415461548857958</v>
+      </c>
+      <c r="G6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1549.3956576058936</v>
-      </c>
-      <c r="F6" s="30">
-        <f t="shared" si="3"/>
-        <v>0.7551331348171384</v>
-      </c>
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="str">
+      <c r="A7" s="28" t="str">
         <f>Nd!A7</f>
         <v>V5</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="33">
         <f>Nd!H7</f>
         <v>975</v>
       </c>
-      <c r="C7" s="33">
-        <f>weld_y!E7*weld_y!G7/100</f>
-        <v>46.367999999999995</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="30">
+        <f>gpl_y!E7</f>
+        <v>48.32</v>
+      </c>
+      <c r="D7" s="7">
+        <v>490</v>
+      </c>
+      <c r="E7" s="33">
         <f t="shared" si="0"/>
-        <v>282.90163190291662</v>
-      </c>
-      <c r="E7" s="27">
+        <v>2367.6799999999998</v>
+      </c>
+      <c r="F7" s="35">
+        <f t="shared" si="2"/>
+        <v>0.41179551290714966</v>
+      </c>
+      <c r="G7" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>1311.7582868074437</v>
-      </c>
-      <c r="F7" s="30">
-        <f t="shared" si="3"/>
-        <v>0.74327717980189345</v>
-      </c>
-      <c r="G7" s="4" t="str">
-        <f t="shared" si="2"/>
         <v>OK</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="str">
+      <c r="A8" s="28" t="str">
         <f>Nd!A8</f>
         <v>V11</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="33">
         <f>Nd!H8</f>
         <v>5343.36</v>
       </c>
-      <c r="C8" s="33">
-        <f>weld_y!E8*weld_y!G8/100</f>
-        <v>237.5</v>
-      </c>
-      <c r="D8" s="5">
-        <f>490/SQRT(3)</f>
-        <v>282.90163190291662</v>
-      </c>
-      <c r="E8" s="27">
-        <f t="shared" ref="E8" si="4">D8*C8*100/1000</f>
-        <v>6718.9137576942694</v>
-      </c>
-      <c r="F8" s="30">
-        <f t="shared" ref="F8" si="5">B8/E8</f>
-        <v>0.79527140735821578</v>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f t="shared" si="2"/>
+      <c r="C8" s="30">
+        <f>gpl_y!E8</f>
+        <v>138</v>
+      </c>
+      <c r="D8" s="7">
+        <v>490</v>
+      </c>
+      <c r="E8" s="33">
+        <f t="shared" ref="E8" si="3">D8*C8*100/1000</f>
+        <v>6762</v>
+      </c>
+      <c r="F8" s="35">
+        <f t="shared" ref="F8" si="4">B8/E8</f>
+        <v>0.79020408163265299</v>
+      </c>
+      <c r="G8" s="7" t="str">
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="G2:G8">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="NG">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="NG">
       <formula>NOT(ISERROR(SEARCH("NG",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
